--- a/Financial Analysis/HON.xlsx
+++ b/Financial Analysis/HON.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1F5363-6C60-4B23-9782-1928FBAFA41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6690B280-04DD-4A0D-AB24-F472CD844BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F30574C2-14C5-4405-B92F-D72ACFF190E8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>HON</t>
   </si>
@@ -197,6 +197,36 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -700,14 +730,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>198.32</v>
+        <v>227</v>
       </c>
       <c r="E3" s="4">
         <v>45770</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45805</v>
       </c>
       <c r="G3" s="4">
         <v>45776</v>
@@ -731,7 +761,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>128888.16799999999</v>
+        <v>147527.29999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -773,7 +803,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>149034.16800000001</v>
+        <v>167673.29999999999</v>
       </c>
     </row>
   </sheetData>
@@ -783,12 +813,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1001FB57-91F3-4052-BB69-223C5CE863B6}">
-  <dimension ref="B2:AJ35"/>
+  <dimension ref="B2:EF35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="37" width="8.88671875" style="1"/>
+    <col min="38" max="38" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.109375" style="1" customWidth="1"/>
+    <col min="40" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:36" x14ac:dyDescent="0.3">
@@ -914,6 +947,50 @@
       <c r="Y3" s="6">
         <v>26279</v>
       </c>
+      <c r="Z3" s="6">
+        <f>Y3*1.01</f>
+        <v>26541.79</v>
+      </c>
+      <c r="AA3" s="6">
+        <f t="shared" ref="AA3:AJ3" si="0">Z3*1.01</f>
+        <v>26807.207900000001</v>
+      </c>
+      <c r="AB3" s="6">
+        <f t="shared" si="0"/>
+        <v>27075.279979000003</v>
+      </c>
+      <c r="AC3" s="6">
+        <f t="shared" si="0"/>
+        <v>27346.032778790002</v>
+      </c>
+      <c r="AD3" s="6">
+        <f t="shared" si="0"/>
+        <v>27619.493106577902</v>
+      </c>
+      <c r="AE3" s="6">
+        <f t="shared" si="0"/>
+        <v>27895.688037643682</v>
+      </c>
+      <c r="AF3" s="6">
+        <f t="shared" si="0"/>
+        <v>28174.64491802012</v>
+      </c>
+      <c r="AG3" s="6">
+        <f t="shared" si="0"/>
+        <v>28456.391367200322</v>
+      </c>
+      <c r="AH3" s="6">
+        <f t="shared" si="0"/>
+        <v>28740.955280872324</v>
+      </c>
+      <c r="AI3" s="6">
+        <f t="shared" si="0"/>
+        <v>29028.364833681047</v>
+      </c>
+      <c r="AJ3" s="6">
+        <f t="shared" si="0"/>
+        <v>29318.648482017859</v>
+      </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -937,34 +1014,122 @@
       <c r="Y4" s="6">
         <v>12219</v>
       </c>
+      <c r="Z4" s="6">
+        <f>Y4*1.08</f>
+        <v>13196.52</v>
+      </c>
+      <c r="AA4" s="6">
+        <f>Z4*1.05</f>
+        <v>13856.346000000001</v>
+      </c>
+      <c r="AB4" s="6">
+        <f>AA4*1.04</f>
+        <v>14410.599840000003</v>
+      </c>
+      <c r="AC4" s="6">
+        <f>AB4*1.03</f>
+        <v>14842.917835200004</v>
+      </c>
+      <c r="AD4" s="6">
+        <f>AC4*1.02</f>
+        <v>15139.776191904004</v>
+      </c>
+      <c r="AE4" s="6">
+        <f t="shared" ref="AE4:AJ4" si="1">AD4*1.02</f>
+        <v>15442.571715742084</v>
+      </c>
+      <c r="AF4" s="6">
+        <f t="shared" si="1"/>
+        <v>15751.423150056926</v>
+      </c>
+      <c r="AG4" s="6">
+        <f t="shared" si="1"/>
+        <v>16066.451613058065</v>
+      </c>
+      <c r="AH4" s="6">
+        <f t="shared" si="1"/>
+        <v>16387.780645319228</v>
+      </c>
+      <c r="AI4" s="6">
+        <f t="shared" si="1"/>
+        <v>16715.536258225613</v>
+      </c>
+      <c r="AJ4" s="6">
+        <f t="shared" si="1"/>
+        <v>17049.846983390125</v>
+      </c>
     </row>
     <row r="5" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" ref="T5:Y5" si="0">T3+T4</f>
+        <f t="shared" ref="T5:Z5" si="2">T3+T4</f>
         <v>36709</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>32637</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>34392</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>35466</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>36662</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>38498</v>
+      </c>
+      <c r="Z5" s="9">
+        <f t="shared" si="2"/>
+        <v>39738.31</v>
+      </c>
+      <c r="AA5" s="9">
+        <f t="shared" ref="AA5:AJ5" si="3">AA3+AA4</f>
+        <v>40663.553899999999</v>
+      </c>
+      <c r="AB5" s="9">
+        <f t="shared" si="3"/>
+        <v>41485.879819000009</v>
+      </c>
+      <c r="AC5" s="9">
+        <f t="shared" si="3"/>
+        <v>42188.950613990004</v>
+      </c>
+      <c r="AD5" s="9">
+        <f t="shared" si="3"/>
+        <v>42759.269298481908</v>
+      </c>
+      <c r="AE5" s="9">
+        <f t="shared" si="3"/>
+        <v>43338.259753385762</v>
+      </c>
+      <c r="AF5" s="9">
+        <f t="shared" si="3"/>
+        <v>43926.068068077046</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="shared" si="3"/>
+        <v>44522.842980258385</v>
+      </c>
+      <c r="AH5" s="9">
+        <f t="shared" si="3"/>
+        <v>45128.735926191555</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" si="3"/>
+        <v>45743.901091906664</v>
+      </c>
+      <c r="AJ5" s="9">
+        <f t="shared" si="3"/>
+        <v>46368.495465407985</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -989,6 +1154,50 @@
       <c r="Y6" s="6">
         <v>17227</v>
       </c>
+      <c r="Z6" s="6">
+        <f>Z3*0.66</f>
+        <v>17517.581400000003</v>
+      </c>
+      <c r="AA6" s="6">
+        <f t="shared" ref="AA6:AJ6" si="4">AA3*0.66</f>
+        <v>17692.757214000001</v>
+      </c>
+      <c r="AB6" s="6">
+        <f t="shared" si="4"/>
+        <v>17869.684786140002</v>
+      </c>
+      <c r="AC6" s="6">
+        <f t="shared" si="4"/>
+        <v>18048.381634001402</v>
+      </c>
+      <c r="AD6" s="6">
+        <f t="shared" si="4"/>
+        <v>18228.865450341415</v>
+      </c>
+      <c r="AE6" s="6">
+        <f t="shared" si="4"/>
+        <v>18411.154104844831</v>
+      </c>
+      <c r="AF6" s="6">
+        <f t="shared" si="4"/>
+        <v>18595.26564589328</v>
+      </c>
+      <c r="AG6" s="6">
+        <f t="shared" si="4"/>
+        <v>18781.218302352212</v>
+      </c>
+      <c r="AH6" s="6">
+        <f t="shared" si="4"/>
+        <v>18969.030485375733</v>
+      </c>
+      <c r="AI6" s="6">
+        <f t="shared" si="4"/>
+        <v>19158.720790229494</v>
+      </c>
+      <c r="AJ6" s="6">
+        <f t="shared" si="4"/>
+        <v>19350.30799813179</v>
+      </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -1012,34 +1221,122 @@
       <c r="Y7" s="6">
         <v>6609</v>
       </c>
+      <c r="Z7" s="6">
+        <f>Z4*0.53</f>
+        <v>6994.155600000001</v>
+      </c>
+      <c r="AA7" s="6">
+        <f t="shared" ref="AA7:AJ7" si="5">AA4*0.53</f>
+        <v>7343.8633800000007</v>
+      </c>
+      <c r="AB7" s="6">
+        <f t="shared" si="5"/>
+        <v>7637.6179152000013</v>
+      </c>
+      <c r="AC7" s="6">
+        <f t="shared" si="5"/>
+        <v>7866.7464526560025</v>
+      </c>
+      <c r="AD7" s="6">
+        <f t="shared" si="5"/>
+        <v>8024.081381709123</v>
+      </c>
+      <c r="AE7" s="6">
+        <f t="shared" si="5"/>
+        <v>8184.5630093433047</v>
+      </c>
+      <c r="AF7" s="6">
+        <f t="shared" si="5"/>
+        <v>8348.2542695301709</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" si="5"/>
+        <v>8515.219354920775</v>
+      </c>
+      <c r="AH7" s="6">
+        <f t="shared" si="5"/>
+        <v>8685.5237420191916</v>
+      </c>
+      <c r="AI7" s="6">
+        <f t="shared" si="5"/>
+        <v>8859.2342168595751</v>
+      </c>
+      <c r="AJ7" s="6">
+        <f t="shared" si="5"/>
+        <v>9036.4189011967665</v>
+      </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="T8" s="6">
-        <f t="shared" ref="T8:Y8" si="1">T6+T7</f>
+        <f t="shared" ref="T8:Y8" si="6">T6+T7</f>
         <v>24339</v>
       </c>
       <c r="U8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>22169</v>
       </c>
       <c r="V8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>23394</v>
       </c>
       <c r="W8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>22347</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>22995</v>
       </c>
       <c r="Y8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>23836</v>
+      </c>
+      <c r="Z8" s="6">
+        <f t="shared" ref="Z8:AJ8" si="7">Z6+Z7</f>
+        <v>24511.737000000005</v>
+      </c>
+      <c r="AA8" s="6">
+        <f t="shared" si="7"/>
+        <v>25036.620594</v>
+      </c>
+      <c r="AB8" s="6">
+        <f t="shared" si="7"/>
+        <v>25507.302701340002</v>
+      </c>
+      <c r="AC8" s="6">
+        <f t="shared" si="7"/>
+        <v>25915.128086657405</v>
+      </c>
+      <c r="AD8" s="6">
+        <f t="shared" si="7"/>
+        <v>26252.946832050537</v>
+      </c>
+      <c r="AE8" s="6">
+        <f t="shared" si="7"/>
+        <v>26595.717114188134</v>
+      </c>
+      <c r="AF8" s="6">
+        <f t="shared" si="7"/>
+        <v>26943.519915423451</v>
+      </c>
+      <c r="AG8" s="6">
+        <f t="shared" si="7"/>
+        <v>27296.437657272989</v>
+      </c>
+      <c r="AH8" s="6">
+        <f t="shared" si="7"/>
+        <v>27654.554227394925</v>
+      </c>
+      <c r="AI8" s="6">
+        <f t="shared" si="7"/>
+        <v>28017.955007089069</v>
+      </c>
+      <c r="AJ8" s="6">
+        <f t="shared" si="7"/>
+        <v>28386.726899328554</v>
       </c>
     </row>
     <row r="9" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1047,28 +1344,72 @@
         <v>18</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9:Y9" si="2">T5-T8</f>
+        <f t="shared" ref="T9:Y9" si="8">T5-T8</f>
         <v>12370</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>10468</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>10998</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>13119</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>13667</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>14662</v>
+      </c>
+      <c r="Z9" s="9">
+        <f t="shared" ref="Z9:AJ9" si="9">Z5-Z8</f>
+        <v>15226.572999999993</v>
+      </c>
+      <c r="AA9" s="9">
+        <f t="shared" si="9"/>
+        <v>15626.933305999999</v>
+      </c>
+      <c r="AB9" s="9">
+        <f t="shared" si="9"/>
+        <v>15978.577117660006</v>
+      </c>
+      <c r="AC9" s="9">
+        <f t="shared" si="9"/>
+        <v>16273.822527332599</v>
+      </c>
+      <c r="AD9" s="9">
+        <f t="shared" si="9"/>
+        <v>16506.322466431371</v>
+      </c>
+      <c r="AE9" s="9">
+        <f t="shared" si="9"/>
+        <v>16742.542639197629</v>
+      </c>
+      <c r="AF9" s="9">
+        <f t="shared" si="9"/>
+        <v>16982.548152653595</v>
+      </c>
+      <c r="AG9" s="9">
+        <f t="shared" si="9"/>
+        <v>17226.405322985396</v>
+      </c>
+      <c r="AH9" s="9">
+        <f t="shared" si="9"/>
+        <v>17474.18169879663</v>
+      </c>
+      <c r="AI9" s="9">
+        <f t="shared" si="9"/>
+        <v>17725.946084817595</v>
+      </c>
+      <c r="AJ9" s="9">
+        <f t="shared" si="9"/>
+        <v>17981.76856607943</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1087,6 +1428,50 @@
       <c r="Y10" s="6">
         <v>1536</v>
       </c>
+      <c r="Z10" s="6">
+        <f>Y10*1.03</f>
+        <v>1582.08</v>
+      </c>
+      <c r="AA10" s="6">
+        <f>Z10*1.02</f>
+        <v>1613.7215999999999</v>
+      </c>
+      <c r="AB10" s="6">
+        <f t="shared" ref="AB10:AJ10" si="10">AA10*1.02</f>
+        <v>1645.9960319999998</v>
+      </c>
+      <c r="AC10" s="6">
+        <f t="shared" si="10"/>
+        <v>1678.9159526399999</v>
+      </c>
+      <c r="AD10" s="6">
+        <f t="shared" si="10"/>
+        <v>1712.4942716927999</v>
+      </c>
+      <c r="AE10" s="6">
+        <f t="shared" si="10"/>
+        <v>1746.7441571266559</v>
+      </c>
+      <c r="AF10" s="6">
+        <f t="shared" si="10"/>
+        <v>1781.679040269189</v>
+      </c>
+      <c r="AG10" s="6">
+        <f t="shared" si="10"/>
+        <v>1817.3126210745729</v>
+      </c>
+      <c r="AH10" s="6">
+        <f t="shared" si="10"/>
+        <v>1853.6588734960644</v>
+      </c>
+      <c r="AI10" s="6">
+        <f t="shared" si="10"/>
+        <v>1890.7320509659858</v>
+      </c>
+      <c r="AJ10" s="6">
+        <f t="shared" si="10"/>
+        <v>1928.5466919853054</v>
+      </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
@@ -1110,6 +1495,50 @@
       <c r="Y11" s="6">
         <v>5466</v>
       </c>
+      <c r="Z11" s="6">
+        <f>Y11*1.03</f>
+        <v>5629.9800000000005</v>
+      </c>
+      <c r="AA11" s="6">
+        <f>Z11*1.02</f>
+        <v>5742.5796000000009</v>
+      </c>
+      <c r="AB11" s="6">
+        <f>AA11*1.01</f>
+        <v>5800.0053960000014</v>
+      </c>
+      <c r="AC11" s="6">
+        <f t="shared" ref="AC11:AJ11" si="11">AB11*1.01</f>
+        <v>5858.0054499600019</v>
+      </c>
+      <c r="AD11" s="6">
+        <f t="shared" si="11"/>
+        <v>5916.5855044596019</v>
+      </c>
+      <c r="AE11" s="6">
+        <f t="shared" si="11"/>
+        <v>5975.7513595041983</v>
+      </c>
+      <c r="AF11" s="6">
+        <f t="shared" si="11"/>
+        <v>6035.5088730992402</v>
+      </c>
+      <c r="AG11" s="6">
+        <f t="shared" si="11"/>
+        <v>6095.8639618302323</v>
+      </c>
+      <c r="AH11" s="6">
+        <f t="shared" si="11"/>
+        <v>6156.8226014485344</v>
+      </c>
+      <c r="AI11" s="6">
+        <f t="shared" si="11"/>
+        <v>6218.3908274630203</v>
+      </c>
+      <c r="AJ11" s="6">
+        <f t="shared" si="11"/>
+        <v>6280.5747357376504</v>
+      </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -1133,34 +1562,111 @@
       <c r="Y12" s="6">
         <v>219</v>
       </c>
+      <c r="Z12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" ref="T13:Y13" si="3">SUM(T10:T12)</f>
+        <f t="shared" ref="T13:Y13" si="12">SUM(T10:T12)</f>
         <v>5519</v>
       </c>
       <c r="U13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>4772</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>4798</v>
       </c>
       <c r="W13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>6692</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>6583</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>7221</v>
+      </c>
+      <c r="Z13" s="6">
+        <f t="shared" ref="Z13:AJ13" si="13">SUM(Z10:Z12)</f>
+        <v>7212.06</v>
+      </c>
+      <c r="AA13" s="6">
+        <f t="shared" si="13"/>
+        <v>7356.3012000000008</v>
+      </c>
+      <c r="AB13" s="6">
+        <f t="shared" si="13"/>
+        <v>7446.0014280000014</v>
+      </c>
+      <c r="AC13" s="6">
+        <f t="shared" si="13"/>
+        <v>7536.9214026000018</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" si="13"/>
+        <v>7629.0797761524018</v>
+      </c>
+      <c r="AE13" s="6">
+        <f t="shared" si="13"/>
+        <v>7722.4955166308537</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="13"/>
+        <v>7817.1879133684288</v>
+      </c>
+      <c r="AG13" s="6">
+        <f t="shared" si="13"/>
+        <v>7913.1765829048054</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="13"/>
+        <v>8010.4814749445986</v>
+      </c>
+      <c r="AI13" s="6">
+        <f t="shared" si="13"/>
+        <v>8109.1228784290061</v>
+      </c>
+      <c r="AJ13" s="6">
+        <f t="shared" si="13"/>
+        <v>8209.1214277229556</v>
       </c>
     </row>
     <row r="14" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1168,28 +1674,72 @@
         <v>24</v>
       </c>
       <c r="T14" s="9">
-        <f t="shared" ref="T14:Y14" si="4">T9-T13</f>
+        <f t="shared" ref="T14:Y14" si="14">T9-T13</f>
         <v>6851</v>
       </c>
       <c r="U14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>5696</v>
       </c>
       <c r="V14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>6200</v>
       </c>
       <c r="W14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>6427</v>
       </c>
       <c r="X14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>7084</v>
       </c>
       <c r="Y14" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>7441</v>
+      </c>
+      <c r="Z14" s="9">
+        <f t="shared" ref="Z14:AJ14" si="15">Z9-Z13</f>
+        <v>8014.5129999999926</v>
+      </c>
+      <c r="AA14" s="9">
+        <f t="shared" si="15"/>
+        <v>8270.6321059999973</v>
+      </c>
+      <c r="AB14" s="9">
+        <f t="shared" si="15"/>
+        <v>8532.5756896600051</v>
+      </c>
+      <c r="AC14" s="9">
+        <f t="shared" si="15"/>
+        <v>8736.901124732598</v>
+      </c>
+      <c r="AD14" s="9">
+        <f t="shared" si="15"/>
+        <v>8877.2426902789703</v>
+      </c>
+      <c r="AE14" s="9">
+        <f t="shared" si="15"/>
+        <v>9020.0471225667752</v>
+      </c>
+      <c r="AF14" s="9">
+        <f t="shared" si="15"/>
+        <v>9165.3602392851662</v>
+      </c>
+      <c r="AG14" s="9">
+        <f t="shared" si="15"/>
+        <v>9313.2287400805908</v>
+      </c>
+      <c r="AH14" s="9">
+        <f t="shared" si="15"/>
+        <v>9463.7002238520327</v>
+      </c>
+      <c r="AI14" s="9">
+        <f t="shared" si="15"/>
+        <v>9616.823206388588</v>
+      </c>
+      <c r="AJ14" s="9">
+        <f t="shared" si="15"/>
+        <v>9772.6471383564749</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.3">
@@ -1214,6 +1764,50 @@
       <c r="Y15" s="6">
         <v>-830</v>
       </c>
+      <c r="Z15" s="6">
+        <f>Y15*1.01</f>
+        <v>-838.3</v>
+      </c>
+      <c r="AA15" s="6">
+        <f t="shared" ref="AA15:AJ15" si="16">Z15*1.01</f>
+        <v>-846.68299999999999</v>
+      </c>
+      <c r="AB15" s="6">
+        <f t="shared" si="16"/>
+        <v>-855.14982999999995</v>
+      </c>
+      <c r="AC15" s="6">
+        <f t="shared" si="16"/>
+        <v>-863.7013283</v>
+      </c>
+      <c r="AD15" s="6">
+        <f t="shared" si="16"/>
+        <v>-872.33834158299999</v>
+      </c>
+      <c r="AE15" s="6">
+        <f t="shared" si="16"/>
+        <v>-881.06172499882996</v>
+      </c>
+      <c r="AF15" s="6">
+        <f t="shared" si="16"/>
+        <v>-889.87234224881831</v>
+      </c>
+      <c r="AG15" s="6">
+        <f t="shared" si="16"/>
+        <v>-898.77106567130647</v>
+      </c>
+      <c r="AH15" s="6">
+        <f t="shared" si="16"/>
+        <v>-907.75877632801951</v>
+      </c>
+      <c r="AI15" s="6">
+        <f t="shared" si="16"/>
+        <v>-916.83636409129974</v>
+      </c>
+      <c r="AJ15" s="6">
+        <f t="shared" si="16"/>
+        <v>-926.0047277322127</v>
+      </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
@@ -1237,66 +1831,198 @@
       <c r="Y16" s="6">
         <v>1058</v>
       </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z16" s="6">
+        <f>Y16*1.02</f>
+        <v>1079.1600000000001</v>
+      </c>
+      <c r="AA16" s="6">
+        <f t="shared" ref="AA16:AJ16" si="17">Z16*1.02</f>
+        <v>1100.7432000000001</v>
+      </c>
+      <c r="AB16" s="6">
+        <f t="shared" si="17"/>
+        <v>1122.7580640000001</v>
+      </c>
+      <c r="AC16" s="6">
+        <f t="shared" si="17"/>
+        <v>1145.2132252800002</v>
+      </c>
+      <c r="AD16" s="6">
+        <f t="shared" si="17"/>
+        <v>1168.1174897856001</v>
+      </c>
+      <c r="AE16" s="6">
+        <f t="shared" si="17"/>
+        <v>1191.4798395813123</v>
+      </c>
+      <c r="AF16" s="6">
+        <f t="shared" si="17"/>
+        <v>1215.3094363729385</v>
+      </c>
+      <c r="AG16" s="6">
+        <f t="shared" si="17"/>
+        <v>1239.6156251003974</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="17"/>
+        <v>1264.4079376024054</v>
+      </c>
+      <c r="AI16" s="6">
+        <f t="shared" si="17"/>
+        <v>1289.6960963544534</v>
+      </c>
+      <c r="AJ16" s="6">
+        <f t="shared" si="17"/>
+        <v>1315.4900182815425</v>
+      </c>
+    </row>
+    <row r="17" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="T17" s="6">
-        <f t="shared" ref="T17:Y17" si="5">SUM(T15:T16)</f>
+        <f t="shared" ref="T17:Y17" si="18">SUM(T15:T16)</f>
         <v>-708</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>-316</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>-1035</v>
       </c>
       <c r="W17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>48</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>-75</v>
       </c>
       <c r="Y17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>228</v>
       </c>
-    </row>
-    <row r="18" spans="2:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Z17" s="6">
+        <f t="shared" ref="Z17:AJ17" si="19">SUM(Z15:Z16)</f>
+        <v>240.86000000000013</v>
+      </c>
+      <c r="AA17" s="6">
+        <f t="shared" si="19"/>
+        <v>254.06020000000012</v>
+      </c>
+      <c r="AB17" s="6">
+        <f t="shared" si="19"/>
+        <v>267.60823400000015</v>
+      </c>
+      <c r="AC17" s="6">
+        <f t="shared" si="19"/>
+        <v>281.51189698000019</v>
+      </c>
+      <c r="AD17" s="6">
+        <f t="shared" si="19"/>
+        <v>295.77914820260014</v>
+      </c>
+      <c r="AE17" s="6">
+        <f t="shared" si="19"/>
+        <v>310.4181145824823</v>
+      </c>
+      <c r="AF17" s="6">
+        <f t="shared" si="19"/>
+        <v>325.43709412412022</v>
+      </c>
+      <c r="AG17" s="6">
+        <f t="shared" si="19"/>
+        <v>340.84455942909096</v>
+      </c>
+      <c r="AH17" s="6">
+        <f t="shared" si="19"/>
+        <v>356.64916127438585</v>
+      </c>
+      <c r="AI17" s="6">
+        <f t="shared" si="19"/>
+        <v>372.85973226315366</v>
+      </c>
+      <c r="AJ17" s="6">
+        <f t="shared" si="19"/>
+        <v>389.48529054932976</v>
+      </c>
+    </row>
+    <row r="18" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18:Y18" si="6">T14-T17</f>
+        <f t="shared" ref="T18:Y18" si="20">T14-T17</f>
         <v>7559</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>6012</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>7235</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>6379</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>7159</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>7213</v>
       </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z18" s="9">
+        <f t="shared" ref="Z18:AJ18" si="21">Z14-Z17</f>
+        <v>7773.652999999993</v>
+      </c>
+      <c r="AA18" s="9">
+        <f t="shared" si="21"/>
+        <v>8016.5719059999974</v>
+      </c>
+      <c r="AB18" s="9">
+        <f t="shared" si="21"/>
+        <v>8264.9674556600057</v>
+      </c>
+      <c r="AC18" s="9">
+        <f t="shared" si="21"/>
+        <v>8455.3892277525974</v>
+      </c>
+      <c r="AD18" s="9">
+        <f t="shared" si="21"/>
+        <v>8581.4635420763698</v>
+      </c>
+      <c r="AE18" s="9">
+        <f t="shared" si="21"/>
+        <v>8709.6290079842929</v>
+      </c>
+      <c r="AF18" s="9">
+        <f t="shared" si="21"/>
+        <v>8839.9231451610467</v>
+      </c>
+      <c r="AG18" s="9">
+        <f t="shared" si="21"/>
+        <v>8972.3841806514993</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" si="21"/>
+        <v>9107.051062577646</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" si="21"/>
+        <v>9243.963474125434</v>
+      </c>
+      <c r="AJ18" s="9">
+        <f t="shared" si="21"/>
+        <v>9383.161847807145</v>
+      </c>
+    </row>
+    <row r="19" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1318,8 +2044,52 @@
       <c r="Y19" s="6">
         <v>1473</v>
       </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z19" s="6">
+        <f>Z18*0.21</f>
+        <v>1632.4671299999984</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" ref="AA19:AJ19" si="22">AA18*0.21</f>
+        <v>1683.4801002599993</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="22"/>
+        <v>1735.6431656886011</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="22"/>
+        <v>1775.6317378280453</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="22"/>
+        <v>1802.1073438360377</v>
+      </c>
+      <c r="AE19" s="6">
+        <f t="shared" si="22"/>
+        <v>1829.0220916767014</v>
+      </c>
+      <c r="AF19" s="6">
+        <f t="shared" si="22"/>
+        <v>1856.3838604838197</v>
+      </c>
+      <c r="AG19" s="6">
+        <f t="shared" si="22"/>
+        <v>1884.2006779368148</v>
+      </c>
+      <c r="AH19" s="6">
+        <f t="shared" si="22"/>
+        <v>1912.4807231413056</v>
+      </c>
+      <c r="AI19" s="6">
+        <f t="shared" si="22"/>
+        <v>1941.2323295663411</v>
+      </c>
+      <c r="AJ19" s="6">
+        <f t="shared" si="22"/>
+        <v>1970.4639880395005</v>
+      </c>
+    </row>
+    <row r="20" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1341,260 +2111,1122 @@
       <c r="Y20" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="2:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Z20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21:Y21" si="7">T18-T19-T20</f>
+        <f t="shared" ref="T21:Y21" si="23">T18-T19-T20</f>
         <v>6143</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="23"/>
         <v>4779</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="23"/>
         <v>5542</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="23"/>
         <v>4966</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="23"/>
         <v>5658</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="23"/>
         <v>5705</v>
       </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z21" s="9">
+        <f t="shared" ref="Z21:AJ21" si="24">Z18-Z19-Z20</f>
+        <v>6141.1858699999948</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="24"/>
+        <v>6333.0918057399977</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="24"/>
+        <v>6529.3242899714041</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="24"/>
+        <v>6679.7574899245519</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="24"/>
+        <v>6779.3561982403317</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="24"/>
+        <v>6880.6069163075917</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" si="24"/>
+        <v>6983.5392846772265</v>
+      </c>
+      <c r="AG21" s="9">
+        <f t="shared" si="24"/>
+        <v>7088.1835027146844</v>
+      </c>
+      <c r="AH21" s="9">
+        <f t="shared" si="24"/>
+        <v>7194.5703394363409</v>
+      </c>
+      <c r="AI21" s="9">
+        <f t="shared" si="24"/>
+        <v>7302.7311445590931</v>
+      </c>
+      <c r="AJ21" s="9">
+        <f t="shared" si="24"/>
+        <v>7412.6978597676443</v>
+      </c>
+      <c r="AK21" s="2">
+        <f>AJ21*(1+$AM$26)</f>
+        <v>7338.5708811699678</v>
+      </c>
+      <c r="AL21" s="2">
+        <f t="shared" ref="AL21:CW21" si="25">AK21*(1+$AM$26)</f>
+        <v>7265.1851723582677</v>
+      </c>
+      <c r="AM21" s="2">
+        <f t="shared" si="25"/>
+        <v>7192.533320634685</v>
+      </c>
+      <c r="AN21" s="2">
+        <f t="shared" si="25"/>
+        <v>7120.6079874283378</v>
+      </c>
+      <c r="AO21" s="2">
+        <f t="shared" si="25"/>
+        <v>7049.4019075540546</v>
+      </c>
+      <c r="AP21" s="2">
+        <f t="shared" si="25"/>
+        <v>6978.907888478514</v>
+      </c>
+      <c r="AQ21" s="2">
+        <f t="shared" si="25"/>
+        <v>6909.1188095937287</v>
+      </c>
+      <c r="AR21" s="2">
+        <f t="shared" si="25"/>
+        <v>6840.0276214977912</v>
+      </c>
+      <c r="AS21" s="2">
+        <f t="shared" si="25"/>
+        <v>6771.6273452828136</v>
+      </c>
+      <c r="AT21" s="2">
+        <f t="shared" si="25"/>
+        <v>6703.9110718299853</v>
+      </c>
+      <c r="AU21" s="2">
+        <f t="shared" si="25"/>
+        <v>6636.8719611116858</v>
+      </c>
+      <c r="AV21" s="2">
+        <f t="shared" si="25"/>
+        <v>6570.5032415005689</v>
+      </c>
+      <c r="AW21" s="2">
+        <f t="shared" si="25"/>
+        <v>6504.798209085563</v>
+      </c>
+      <c r="AX21" s="2">
+        <f t="shared" si="25"/>
+        <v>6439.7502269947072</v>
+      </c>
+      <c r="AY21" s="2">
+        <f t="shared" si="25"/>
+        <v>6375.3527247247603</v>
+      </c>
+      <c r="AZ21" s="2">
+        <f t="shared" si="25"/>
+        <v>6311.5991974775125</v>
+      </c>
+      <c r="BA21" s="2">
+        <f t="shared" si="25"/>
+        <v>6248.4832055027373</v>
+      </c>
+      <c r="BB21" s="2">
+        <f t="shared" si="25"/>
+        <v>6185.99837344771</v>
+      </c>
+      <c r="BC21" s="2">
+        <f t="shared" si="25"/>
+        <v>6124.1383897132328</v>
+      </c>
+      <c r="BD21" s="2">
+        <f t="shared" si="25"/>
+        <v>6062.8970058161003</v>
+      </c>
+      <c r="BE21" s="2">
+        <f t="shared" si="25"/>
+        <v>6002.2680357579393</v>
+      </c>
+      <c r="BF21" s="2">
+        <f t="shared" si="25"/>
+        <v>5942.2453554003596</v>
+      </c>
+      <c r="BG21" s="2">
+        <f t="shared" si="25"/>
+        <v>5882.8229018463562</v>
+      </c>
+      <c r="BH21" s="2">
+        <f t="shared" si="25"/>
+        <v>5823.9946728278928</v>
+      </c>
+      <c r="BI21" s="2">
+        <f t="shared" si="25"/>
+        <v>5765.7547260996134</v>
+      </c>
+      <c r="BJ21" s="2">
+        <f t="shared" si="25"/>
+        <v>5708.0971788386169</v>
+      </c>
+      <c r="BK21" s="2">
+        <f t="shared" si="25"/>
+        <v>5651.0162070502311</v>
+      </c>
+      <c r="BL21" s="2">
+        <f t="shared" si="25"/>
+        <v>5594.5060449797284</v>
+      </c>
+      <c r="BM21" s="2">
+        <f t="shared" si="25"/>
+        <v>5538.5609845299314</v>
+      </c>
+      <c r="BN21" s="2">
+        <f t="shared" si="25"/>
+        <v>5483.1753746846316</v>
+      </c>
+      <c r="BO21" s="2">
+        <f t="shared" si="25"/>
+        <v>5428.3436209377851</v>
+      </c>
+      <c r="BP21" s="2">
+        <f t="shared" si="25"/>
+        <v>5374.060184728407</v>
+      </c>
+      <c r="BQ21" s="2">
+        <f t="shared" si="25"/>
+        <v>5320.3195828811231</v>
+      </c>
+      <c r="BR21" s="2">
+        <f t="shared" si="25"/>
+        <v>5267.1163870523114</v>
+      </c>
+      <c r="BS21" s="2">
+        <f t="shared" si="25"/>
+        <v>5214.4452231817886</v>
+      </c>
+      <c r="BT21" s="2">
+        <f t="shared" si="25"/>
+        <v>5162.3007709499707</v>
+      </c>
+      <c r="BU21" s="2">
+        <f t="shared" si="25"/>
+        <v>5110.677763240471</v>
+      </c>
+      <c r="BV21" s="2">
+        <f t="shared" si="25"/>
+        <v>5059.5709856080666</v>
+      </c>
+      <c r="BW21" s="2">
+        <f t="shared" si="25"/>
+        <v>5008.9752757519855</v>
+      </c>
+      <c r="BX21" s="2">
+        <f t="shared" si="25"/>
+        <v>4958.8855229944656</v>
+      </c>
+      <c r="BY21" s="2">
+        <f t="shared" si="25"/>
+        <v>4909.2966677645209</v>
+      </c>
+      <c r="BZ21" s="2">
+        <f t="shared" si="25"/>
+        <v>4860.2037010868753</v>
+      </c>
+      <c r="CA21" s="2">
+        <f t="shared" si="25"/>
+        <v>4811.6016640760063</v>
+      </c>
+      <c r="CB21" s="2">
+        <f t="shared" si="25"/>
+        <v>4763.4856474352464</v>
+      </c>
+      <c r="CC21" s="2">
+        <f t="shared" si="25"/>
+        <v>4715.8507909608943</v>
+      </c>
+      <c r="CD21" s="2">
+        <f t="shared" si="25"/>
+        <v>4668.6922830512849</v>
+      </c>
+      <c r="CE21" s="2">
+        <f t="shared" si="25"/>
+        <v>4622.0053602207718</v>
+      </c>
+      <c r="CF21" s="2">
+        <f t="shared" si="25"/>
+        <v>4575.7853066185644</v>
+      </c>
+      <c r="CG21" s="2">
+        <f t="shared" si="25"/>
+        <v>4530.0274535523786</v>
+      </c>
+      <c r="CH21" s="2">
+        <f t="shared" si="25"/>
+        <v>4484.7271790168552</v>
+      </c>
+      <c r="CI21" s="2">
+        <f t="shared" si="25"/>
+        <v>4439.8799072266866</v>
+      </c>
+      <c r="CJ21" s="2">
+        <f t="shared" si="25"/>
+        <v>4395.4811081544194</v>
+      </c>
+      <c r="CK21" s="2">
+        <f t="shared" si="25"/>
+        <v>4351.5262970728754</v>
+      </c>
+      <c r="CL21" s="2">
+        <f t="shared" si="25"/>
+        <v>4308.0110341021464</v>
+      </c>
+      <c r="CM21" s="2">
+        <f t="shared" si="25"/>
+        <v>4264.9309237611251</v>
+      </c>
+      <c r="CN21" s="2">
+        <f t="shared" si="25"/>
+        <v>4222.2816145235138</v>
+      </c>
+      <c r="CO21" s="2">
+        <f t="shared" si="25"/>
+        <v>4180.0587983782789</v>
+      </c>
+      <c r="CP21" s="2">
+        <f t="shared" si="25"/>
+        <v>4138.258210394496</v>
+      </c>
+      <c r="CQ21" s="2">
+        <f t="shared" si="25"/>
+        <v>4096.8756282905506</v>
+      </c>
+      <c r="CR21" s="2">
+        <f t="shared" si="25"/>
+        <v>4055.9068720076452</v>
+      </c>
+      <c r="CS21" s="2">
+        <f t="shared" si="25"/>
+        <v>4015.3478032875687</v>
+      </c>
+      <c r="CT21" s="2">
+        <f t="shared" si="25"/>
+        <v>3975.194325254693</v>
+      </c>
+      <c r="CU21" s="2">
+        <f t="shared" si="25"/>
+        <v>3935.4423820021461</v>
+      </c>
+      <c r="CV21" s="2">
+        <f t="shared" si="25"/>
+        <v>3896.0879581821246</v>
+      </c>
+      <c r="CW21" s="2">
+        <f t="shared" si="25"/>
+        <v>3857.1270786003033</v>
+      </c>
+      <c r="CX21" s="2">
+        <f t="shared" ref="CX21:EF21" si="26">CW21*(1+$AM$26)</f>
+        <v>3818.5558078143004</v>
+      </c>
+      <c r="CY21" s="2">
+        <f t="shared" si="26"/>
+        <v>3780.3702497361573</v>
+      </c>
+      <c r="CZ21" s="2">
+        <f t="shared" si="26"/>
+        <v>3742.5665472387959</v>
+      </c>
+      <c r="DA21" s="2">
+        <f t="shared" si="26"/>
+        <v>3705.1408817664078</v>
+      </c>
+      <c r="DB21" s="2">
+        <f t="shared" si="26"/>
+        <v>3668.0894729487436</v>
+      </c>
+      <c r="DC21" s="2">
+        <f t="shared" si="26"/>
+        <v>3631.408578219256</v>
+      </c>
+      <c r="DD21" s="2">
+        <f t="shared" si="26"/>
+        <v>3595.0944924370633</v>
+      </c>
+      <c r="DE21" s="2">
+        <f t="shared" si="26"/>
+        <v>3559.1435475126927</v>
+      </c>
+      <c r="DF21" s="2">
+        <f t="shared" si="26"/>
+        <v>3523.5521120375656</v>
+      </c>
+      <c r="DG21" s="2">
+        <f t="shared" si="26"/>
+        <v>3488.3165909171898</v>
+      </c>
+      <c r="DH21" s="2">
+        <f t="shared" si="26"/>
+        <v>3453.4334250080178</v>
+      </c>
+      <c r="DI21" s="2">
+        <f t="shared" si="26"/>
+        <v>3418.8990907579378</v>
+      </c>
+      <c r="DJ21" s="2">
+        <f t="shared" si="26"/>
+        <v>3384.7100998503583</v>
+      </c>
+      <c r="DK21" s="2">
+        <f t="shared" si="26"/>
+        <v>3350.8629988518546</v>
+      </c>
+      <c r="DL21" s="2">
+        <f t="shared" si="26"/>
+        <v>3317.3543688633363</v>
+      </c>
+      <c r="DM21" s="2">
+        <f t="shared" si="26"/>
+        <v>3284.1808251747029</v>
+      </c>
+      <c r="DN21" s="2">
+        <f t="shared" si="26"/>
+        <v>3251.339016922956</v>
+      </c>
+      <c r="DO21" s="2">
+        <f t="shared" si="26"/>
+        <v>3218.8256267537263</v>
+      </c>
+      <c r="DP21" s="2">
+        <f t="shared" si="26"/>
+        <v>3186.637370486189</v>
+      </c>
+      <c r="DQ21" s="2">
+        <f t="shared" si="26"/>
+        <v>3154.7709967813271</v>
+      </c>
+      <c r="DR21" s="2">
+        <f t="shared" si="26"/>
+        <v>3123.2232868135138</v>
+      </c>
+      <c r="DS21" s="2">
+        <f t="shared" si="26"/>
+        <v>3091.9910539453786</v>
+      </c>
+      <c r="DT21" s="2">
+        <f t="shared" si="26"/>
+        <v>3061.0711434059249</v>
+      </c>
+      <c r="DU21" s="2">
+        <f t="shared" si="26"/>
+        <v>3030.4604319718655</v>
+      </c>
+      <c r="DV21" s="2">
+        <f t="shared" si="26"/>
+        <v>3000.1558276521469</v>
+      </c>
+      <c r="DW21" s="2">
+        <f t="shared" si="26"/>
+        <v>2970.1542693756255</v>
+      </c>
+      <c r="DX21" s="2">
+        <f t="shared" si="26"/>
+        <v>2940.4527266818691</v>
+      </c>
+      <c r="DY21" s="2">
+        <f t="shared" si="26"/>
+        <v>2911.0481994150505</v>
+      </c>
+      <c r="DZ21" s="2">
+        <f t="shared" si="26"/>
+        <v>2881.9377174208998</v>
+      </c>
+      <c r="EA21" s="2">
+        <f t="shared" si="26"/>
+        <v>2853.1183402466909</v>
+      </c>
+      <c r="EB21" s="2">
+        <f t="shared" si="26"/>
+        <v>2824.587156844224</v>
+      </c>
+      <c r="EC21" s="2">
+        <f t="shared" si="26"/>
+        <v>2796.3412852757815</v>
+      </c>
+      <c r="ED21" s="2">
+        <f t="shared" si="26"/>
+        <v>2768.3778724230237</v>
+      </c>
+      <c r="EE21" s="2">
+        <f t="shared" si="26"/>
+        <v>2740.6940936987935</v>
+      </c>
+      <c r="EF21" s="2">
+        <f t="shared" si="26"/>
+        <v>2713.2871527618054</v>
+      </c>
+    </row>
+    <row r="22" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" ref="T22:Y22" si="8">649.9</f>
+        <f t="shared" ref="T22:AJ22" si="27">649.9</f>
         <v>649.9</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>649.9</v>
       </c>
       <c r="V22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>649.9</v>
       </c>
       <c r="W22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>649.9</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>649.9</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="27"/>
         <v>649.9</v>
       </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AA22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AB22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AC22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AD22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AE22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AF22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AG22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AH22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AI22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+      <c r="AJ22" s="6">
+        <f t="shared" si="27"/>
+        <v>649.9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="T23" s="8">
-        <f t="shared" ref="T23:Y23" si="9">T21/T22</f>
+        <f t="shared" ref="T23:Y23" si="28">T21/T22</f>
         <v>9.4522234189875363</v>
       </c>
       <c r="U23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>7.3534389906139408</v>
       </c>
       <c r="V23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>8.5274657639636864</v>
       </c>
       <c r="W23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>7.6411755654716114</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>8.7059547622711193</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="28"/>
         <v>8.778273580550854</v>
       </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z23" s="8">
+        <f t="shared" ref="Z23:AJ23" si="29">Z21/Z22</f>
+        <v>9.4494320203108089</v>
+      </c>
+      <c r="AA23" s="8">
+        <f t="shared" si="29"/>
+        <v>9.7447173499615296</v>
+      </c>
+      <c r="AB23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.046659932253277</v>
+      </c>
+      <c r="AC23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.278131235458613</v>
+      </c>
+      <c r="AD23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.431383594768937</v>
+      </c>
+      <c r="AE23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.587177898611467</v>
+      </c>
+      <c r="AF23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.745559754850326</v>
+      </c>
+      <c r="AG23" s="8">
+        <f t="shared" si="29"/>
+        <v>10.906575631196622</v>
+      </c>
+      <c r="AH23" s="8">
+        <f t="shared" si="29"/>
+        <v>11.070272871882352</v>
+      </c>
+      <c r="AI23" s="8">
+        <f t="shared" si="29"/>
+        <v>11.2366997146624</v>
+      </c>
+      <c r="AJ23" s="8">
+        <f t="shared" si="29"/>
+        <v>11.405905308151477</v>
+      </c>
+    </row>
+    <row r="25" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
       <c r="T25" s="10"/>
       <c r="U25" s="10">
-        <f t="shared" ref="U25:Y27" si="10">U3/T3-1</f>
+        <f t="shared" ref="U25:Y27" si="30">U3/T3-1</f>
         <v>-0.10467262658800536</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>3.6625298136394813E-2</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>1.2362048122294578E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>-7.2033898305084998E-3</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>1.9632949210413919E-2</v>
       </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z25" s="10">
+        <f t="shared" ref="Z25:Z27" si="31">Z3/Y3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AA25" s="10">
+        <f t="shared" ref="AA25:AA27" si="32">AA3/Z3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AB25" s="10">
+        <f t="shared" ref="AB25:AB27" si="33">AB3/AA3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AC25" s="10">
+        <f t="shared" ref="AC25:AC27" si="34">AC3/AB3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AD25" s="10">
+        <f t="shared" ref="AD25:AD27" si="35">AD3/AC3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AE25" s="10">
+        <f t="shared" ref="AE25:AE27" si="36">AE3/AD3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF25" s="10">
+        <f t="shared" ref="AF25:AF27" si="37">AF3/AE3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG25" s="10">
+        <f t="shared" ref="AG25:AG27" si="38">AG3/AF3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH25" s="10">
+        <f t="shared" ref="AH25:AH27" si="39">AH3/AG3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI25" s="10">
+        <f t="shared" ref="AI25:AI27" si="40">AI3/AH3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ25" s="10">
+        <f t="shared" ref="AJ25:AJ27" si="41">AJ3/AI3-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>-0.12995594713656389</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>0.10746835443037983</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>8.6524174191336067E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>0.14548706080370288</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>0.12214161079988983</v>
       </c>
-    </row>
-    <row r="27" spans="2:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Z26" s="10">
+        <f t="shared" si="31"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AA26" s="10">
+        <f t="shared" si="32"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB26" s="10">
+        <f t="shared" si="33"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AC26" s="10">
+        <f t="shared" si="34"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD26" s="10">
+        <f t="shared" si="35"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE26" s="10">
+        <f t="shared" si="36"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF26" s="10">
+        <f t="shared" si="37"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG26" s="10">
+        <f t="shared" si="38"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH26" s="10">
+        <f t="shared" si="39"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI26" s="10">
+        <f t="shared" si="40"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AJ26" s="10">
+        <f t="shared" si="41"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AL26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM26" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="27" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>49</v>
       </c>
       <c r="T27" s="11"/>
       <c r="U27" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>-0.11092647579612624</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>5.377332475411345E-2</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>3.1228192602930971E-2</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>3.3722438391699194E-2</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="30"/>
         <v>5.0079100976487823E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z27" s="11">
+        <f t="shared" si="31"/>
+        <v>3.2217517793132089E-2</v>
+      </c>
+      <c r="AA27" s="11">
+        <f t="shared" si="32"/>
+        <v>2.3283423477244103E-2</v>
+      </c>
+      <c r="AB27" s="11">
+        <f t="shared" si="33"/>
+        <v>2.0222677069059891E-2</v>
+      </c>
+      <c r="AC27" s="11">
+        <f t="shared" si="34"/>
+        <v>1.6947231155695519E-2</v>
+      </c>
+      <c r="AD27" s="11">
+        <f t="shared" si="35"/>
+        <v>1.3518200291589677E-2</v>
+      </c>
+      <c r="AE27" s="11">
+        <f t="shared" si="36"/>
+        <v>1.3540700400238359E-2</v>
+      </c>
+      <c r="AF27" s="11">
+        <f t="shared" si="37"/>
+        <v>1.3563265300364558E-2</v>
+      </c>
+      <c r="AG27" s="11">
+        <f t="shared" si="38"/>
+        <v>1.358589417237277E-2</v>
+      </c>
+      <c r="AH27" s="11">
+        <f t="shared" si="39"/>
+        <v>1.3608586185788418E-2</v>
+      </c>
+      <c r="AI27" s="11">
+        <f t="shared" si="40"/>
+        <v>1.3631340499348665E-2</v>
+      </c>
+      <c r="AJ27" s="11">
+        <f t="shared" si="41"/>
+        <v>1.3654156261102779E-2</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM27" s="10">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="28" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" ref="T28:Y29" si="11">(T3-T6)/T3</f>
+        <f t="shared" ref="T28:Y29" si="42">(T3-T6)/T3</f>
         <v>0.30258062181041662</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.28697901928285563</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.28463908279062511</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.34687981510015409</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.34128739378419276</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.34445755165721681</v>
       </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z28" s="10">
+        <f t="shared" ref="Z28:AJ28" si="43">(Z3-Z6)/Z3</f>
+        <v>0.33999999999999991</v>
+      </c>
+      <c r="AA28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AB28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AC28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AD28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.34</v>
+      </c>
+      <c r="AE28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AF28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AG28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.34</v>
+      </c>
+      <c r="AH28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.34</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999991</v>
+      </c>
+      <c r="AJ28" s="10">
+        <f t="shared" si="43"/>
+        <v>0.33999999999999991</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM28" s="6">
+        <f>NPV(AM27,Z21:EF21)</f>
+        <v>108619.57438714338</v>
+      </c>
+    </row>
+    <row r="29" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.44162995594713655</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.42645569620253165</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.42279117613441536</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.43277929728592468</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.44733217007989712</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="42"/>
         <v>0.45912104100171863</v>
       </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z29" s="10">
+        <f t="shared" ref="Z29:AJ29" si="44">(Z4-Z7)/Z4</f>
+        <v>0.46999999999999992</v>
+      </c>
+      <c r="AA29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="AB29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="AC29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AD29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.46999999999999992</v>
+      </c>
+      <c r="AE29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AF29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AG29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AH29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AI29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AJ29" s="10">
+        <f t="shared" si="44"/>
+        <v>0.47</v>
+      </c>
+      <c r="AL29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AM29" s="6">
+        <f>Main!D8</f>
+        <v>-20146</v>
+      </c>
+    </row>
+    <row r="30" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" ref="T30:Y30" si="12">T9/T5</f>
+        <f t="shared" ref="T30:Y30" si="45">T9/T5</f>
         <v>0.3369745838895094</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="45"/>
         <v>0.32074026411741274</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="45"/>
         <v>0.31978367062107466</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="45"/>
         <v>0.36990356961597021</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="45"/>
         <v>0.3727838088483989</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="45"/>
         <v>0.38085095329627511</v>
       </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z30" s="10">
+        <f t="shared" ref="Z30:AJ30" si="46">Z9/Z5</f>
+        <v>0.38317112630104283</v>
+      </c>
+      <c r="AA30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38429826729925837</v>
+      </c>
+      <c r="AB30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38515700251202145</v>
+      </c>
+      <c r="AC30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.3857366037906651</v>
+      </c>
+      <c r="AD30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38602910520310035</v>
+      </c>
+      <c r="AE30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38632244890473788</v>
+      </c>
+      <c r="AF30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38661662424084664</v>
+      </c>
+      <c r="AG30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38691162041524746</v>
+      </c>
+      <c r="AH30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38720742649153322</v>
+      </c>
+      <c r="AI30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38750403139433587</v>
+      </c>
+      <c r="AJ30" s="10">
+        <f t="shared" si="46"/>
+        <v>0.38780142391064343</v>
+      </c>
+      <c r="AL30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM30" s="6">
+        <f>AM28+AM29</f>
+        <v>88473.574387143381</v>
+      </c>
+    </row>
+    <row r="31" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>54</v>
       </c>
@@ -1610,22 +3242,73 @@
         <f>Y10/X10-1</f>
         <v>5.4945054945054972E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z31" s="10">
+        <f t="shared" ref="Z31:AJ31" si="47">Z10/Y10-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AA31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AB31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AC31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AJ31" s="10">
+        <f t="shared" si="47"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AL31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM31" s="5">
+        <f>AM30/AJ22</f>
+        <v>136.1341350779249</v>
+      </c>
+    </row>
+    <row r="32" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
       <c r="T32" s="10"/>
       <c r="U32" s="10">
-        <f t="shared" ref="U32:W32" si="13">U11/T11-1</f>
+        <f t="shared" ref="U32:W32" si="48">U11/T11-1</f>
         <v>-0.13535060699402068</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="48"/>
         <v>5.4484492875104262E-3</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="48"/>
         <v>8.6702792830345876E-2</v>
       </c>
       <c r="X32" s="10">
@@ -1636,92 +3319,288 @@
         <f>Y11/X11-1</f>
         <v>6.6120538326506662E-2</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z32" s="10">
+        <f t="shared" ref="Z32:AJ32" si="49">Z11/Y11-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" si="49"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AB32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AC32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AD32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AE32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AJ32" s="10">
+        <f t="shared" si="49"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AL32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM32" s="5">
+        <f>Main!D3</f>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>55</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:Y33" si="14">T14/T5</f>
+        <f t="shared" ref="T33:Y33" si="50">T14/T5</f>
         <v>0.18662998174834508</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0.17452584489996018</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0.18027448243777622</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0.18121581232729939</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0.19322459222082811</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0.19328276793599666</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z33" s="10">
+        <f t="shared" ref="Z33:AJ33" si="51">Z14/Z5</f>
+        <v>0.20168228090223245</v>
+      </c>
+      <c r="AA33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20339176763396466</v>
+      </c>
+      <c r="AB33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20567421317535112</v>
+      </c>
+      <c r="AC33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.2070897947823194</v>
+      </c>
+      <c r="AD33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20760978463666452</v>
+      </c>
+      <c r="AE33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20813127185758981</v>
+      </c>
+      <c r="AF33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20865423750381215</v>
+      </c>
+      <c r="AG33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20917866238259122</v>
+      </c>
+      <c r="AH33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.20970452705189876</v>
+      </c>
+      <c r="AI33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.21023181182267081</v>
+      </c>
+      <c r="AJ33" s="10">
+        <f t="shared" si="51"/>
+        <v>0.21076049676114908</v>
+      </c>
+      <c r="AL33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM33" s="11">
+        <f>AM31/AM32-1</f>
+        <v>-0.4002901538417406</v>
+      </c>
+    </row>
+    <row r="34" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" ref="T34:X34" si="15">T19/T18</f>
+        <f t="shared" ref="T34:X34" si="52">T19/T18</f>
         <v>0.1758169069982802</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="52"/>
         <v>0.19078509647371922</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="52"/>
         <v>0.22460262612301313</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="52"/>
         <v>0.22135130898259917</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="52"/>
         <v>0.20771057410252827</v>
       </c>
       <c r="Y34" s="10">
         <f>Y19/Y18</f>
         <v>0.20421461250519896</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Z34" s="10">
+        <f t="shared" ref="Z34:AJ34" si="53">Z19/Z18</f>
+        <v>0.21</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AB34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AD34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AE34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AF34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AG34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AH34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AI34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AJ34" s="10">
+        <f t="shared" si="53"/>
+        <v>0.21</v>
+      </c>
+      <c r="AL34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM34" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" ref="T35:Y35" si="16">T21/T5</f>
+        <f t="shared" ref="T35:Y35" si="54">T21/T5</f>
         <v>0.16734315835353727</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="54"/>
         <v>0.14642889971504733</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="54"/>
         <v>0.16114212607583159</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="54"/>
         <v>0.14002142897422884</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="54"/>
         <v>0.15432873274780426</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="54"/>
         <v>0.1481895163385111</v>
+      </c>
+      <c r="Z35" s="10">
+        <f t="shared" ref="Z35:AJ35" si="55">Z21/Z5</f>
+        <v>0.15454069058296629</v>
+      </c>
+      <c r="AA35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15574368687287801</v>
+      </c>
+      <c r="AB35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15738666549819816</v>
+      </c>
+      <c r="AC35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15832954820425235</v>
+      </c>
+      <c r="AD35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15854705446243489</v>
+      </c>
+      <c r="AE35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15876518705322612</v>
+      </c>
+      <c r="AF35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.1589839380536876</v>
+      </c>
+      <c r="AG35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.159203299435699</v>
+      </c>
+      <c r="AH35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15942326306686552</v>
+      </c>
+      <c r="AI35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15964382071145969</v>
+      </c>
+      <c r="AJ35" s="10">
+        <f t="shared" si="55"/>
+        <v>0.15986496403140135</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/HON.xlsx
+++ b/Financial Analysis/HON.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6690B280-04DD-4A0D-AB24-F472CD844BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74657B5-88B4-4F64-98D6-D66596CE543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F30574C2-14C5-4405-B92F-D72ACFF190E8}"/>
   </bookViews>
@@ -226,7 +226,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -381,6 +381,56 @@
         <a:xfrm>
           <a:off x="16085820" y="0"/>
           <a:ext cx="0" cy="7604760"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0636523D-D7A8-136C-838A-8D31496AE002}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10591800" y="7620"/>
+          <a:ext cx="0" cy="7231380"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -730,17 +780,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>227</v>
+        <v>214.25</v>
       </c>
       <c r="E3" s="4">
-        <v>45770</v>
+        <v>45906</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45805</v>
+        <v>45906</v>
       </c>
       <c r="G3" s="4">
-        <v>45776</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -748,11 +798,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>649.9</f>
-        <v>649.9</v>
+        <f>637.5</f>
+        <v>637.5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -761,7 +811,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>147527.29999999999</v>
+        <v>136584.375</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -769,11 +819,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>10567+386</f>
-        <v>10953</v>
+        <f>10349+328+1427</f>
+        <v>12104</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -781,11 +831,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>4273+1347+25479</f>
-        <v>31099</v>
+        <f>6271+74+30167</f>
+        <v>36512</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -794,7 +844,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-20146</v>
+        <v>-24408</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -803,7 +853,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>167673.29999999999</v>
+        <v>160992.375</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +870,7 @@
     <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="37" width="8.88671875" style="1"/>
     <col min="38" max="38" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -929,6 +979,52 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="6">
+        <v>6132</v>
+      </c>
+      <c r="D3" s="6">
+        <v>6684</v>
+      </c>
+      <c r="G3" s="6">
+        <v>6310</v>
+      </c>
+      <c r="H3" s="6">
+        <v>6441</v>
+      </c>
+      <c r="I3" s="6">
+        <v>6294</v>
+      </c>
+      <c r="J3" s="6">
+        <f>X3-I3-H3-G3</f>
+        <v>6728</v>
+      </c>
+      <c r="K3" s="6">
+        <v>6263</v>
+      </c>
+      <c r="L3" s="6">
+        <v>6477</v>
+      </c>
+      <c r="M3" s="6">
+        <v>6590</v>
+      </c>
+      <c r="N3" s="6">
+        <f>Y3-M3-L3-K3</f>
+        <v>6949</v>
+      </c>
+      <c r="O3" s="6">
+        <v>6645</v>
+      </c>
+      <c r="P3" s="6">
+        <v>7119</v>
+      </c>
+      <c r="Q3" s="6">
+        <f>M3*1.1</f>
+        <v>7249.0000000000009</v>
+      </c>
+      <c r="R3" s="6">
+        <f>N3*1.08</f>
+        <v>7504.92</v>
+      </c>
       <c r="T3" s="6">
         <v>27629</v>
       </c>
@@ -948,54 +1044,100 @@
         <v>26279</v>
       </c>
       <c r="Z3" s="6">
-        <f>Y3*1.01</f>
-        <v>26541.79</v>
+        <f>SUM(O3:R3)</f>
+        <v>28517.919999999998</v>
       </c>
       <c r="AA3" s="6">
-        <f t="shared" ref="AA3:AJ3" si="0">Z3*1.01</f>
-        <v>26807.207900000001</v>
+        <f>Z3*1.06</f>
+        <v>30228.995200000001</v>
       </c>
       <c r="AB3" s="6">
-        <f t="shared" si="0"/>
-        <v>27075.279979000003</v>
+        <f>AA3*1.05</f>
+        <v>31740.444960000004</v>
       </c>
       <c r="AC3" s="6">
-        <f t="shared" si="0"/>
-        <v>27346.032778790002</v>
+        <f>AB3*1.04</f>
+        <v>33010.062758400003</v>
       </c>
       <c r="AD3" s="6">
-        <f t="shared" si="0"/>
-        <v>27619.493106577902</v>
+        <f>AC3*1.03</f>
+        <v>34000.364641152002</v>
       </c>
       <c r="AE3" s="6">
-        <f t="shared" si="0"/>
-        <v>27895.688037643682</v>
+        <f t="shared" ref="AE3" si="0">AD3*1.02</f>
+        <v>34680.371933975046</v>
       </c>
       <c r="AF3" s="6">
-        <f t="shared" si="0"/>
-        <v>28174.64491802012</v>
+        <f t="shared" ref="AF3:AJ3" si="1">AE3*1.01</f>
+        <v>35027.1756533148</v>
       </c>
       <c r="AG3" s="6">
-        <f t="shared" si="0"/>
-        <v>28456.391367200322</v>
+        <f t="shared" si="1"/>
+        <v>35377.447409847948</v>
       </c>
       <c r="AH3" s="6">
-        <f t="shared" si="0"/>
-        <v>28740.955280872324</v>
+        <f t="shared" si="1"/>
+        <v>35731.221883946426</v>
       </c>
       <c r="AI3" s="6">
-        <f t="shared" si="0"/>
-        <v>29028.364833681047</v>
+        <f t="shared" si="1"/>
+        <v>36088.534102785889</v>
       </c>
       <c r="AJ3" s="6">
-        <f t="shared" si="0"/>
-        <v>29318.648482017859</v>
+        <f t="shared" si="1"/>
+        <v>36449.419443813749</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C4" s="6">
+        <v>2244</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2269</v>
+      </c>
+      <c r="G4" s="6">
+        <v>2554</v>
+      </c>
+      <c r="H4" s="6">
+        <v>2705</v>
+      </c>
+      <c r="I4" s="6">
+        <v>2918</v>
+      </c>
+      <c r="J4" s="6">
+        <f>X4-I4-H4-G4</f>
+        <v>2712</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2842</v>
+      </c>
+      <c r="L4" s="6">
+        <v>3100</v>
+      </c>
+      <c r="M4" s="6">
+        <v>3138</v>
+      </c>
+      <c r="N4" s="6">
+        <f>Y4-M4-L4-K4</f>
+        <v>3139</v>
+      </c>
+      <c r="O4" s="6">
+        <v>3177</v>
+      </c>
+      <c r="P4" s="6">
+        <v>3233</v>
+      </c>
+      <c r="Q4" s="6">
+        <f>M4*1.08</f>
+        <v>3389.0400000000004</v>
+      </c>
+      <c r="R4" s="6">
+        <f>N4*1.1</f>
+        <v>3452.9</v>
+      </c>
       <c r="T4" s="6">
         <v>9080</v>
       </c>
@@ -1015,127 +1157,229 @@
         <v>12219</v>
       </c>
       <c r="Z4" s="6">
-        <f>Y4*1.08</f>
-        <v>13196.52</v>
+        <f>SUM(O4:R4)</f>
+        <v>13251.94</v>
       </c>
       <c r="AA4" s="6">
-        <f>Z4*1.05</f>
-        <v>13856.346000000001</v>
+        <f>Z4*1.06</f>
+        <v>14047.056400000001</v>
       </c>
       <c r="AB4" s="6">
-        <f>AA4*1.04</f>
-        <v>14410.599840000003</v>
+        <f>AA4*1.05</f>
+        <v>14749.409220000001</v>
       </c>
       <c r="AC4" s="6">
-        <f>AB4*1.03</f>
-        <v>14842.917835200004</v>
+        <f>AB4*1.04</f>
+        <v>15339.385588800002</v>
       </c>
       <c r="AD4" s="6">
-        <f>AC4*1.02</f>
-        <v>15139.776191904004</v>
+        <f>AC4*1.03</f>
+        <v>15799.567156464002</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" ref="AE4:AJ4" si="1">AD4*1.02</f>
-        <v>15442.571715742084</v>
+        <f>AD4*1.03</f>
+        <v>16273.554171157923</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" si="1"/>
-        <v>15751.423150056926</v>
+        <f t="shared" ref="AF4:AJ4" si="2">AE4*1.02</f>
+        <v>16599.02525458108</v>
       </c>
       <c r="AG4" s="6">
-        <f t="shared" si="1"/>
-        <v>16066.451613058065</v>
+        <f t="shared" si="2"/>
+        <v>16931.005759672702</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="1"/>
-        <v>16387.780645319228</v>
+        <f t="shared" si="2"/>
+        <v>17269.625874866157</v>
       </c>
       <c r="AI4" s="6">
-        <f t="shared" si="1"/>
-        <v>16715.536258225613</v>
+        <f t="shared" si="2"/>
+        <v>17615.01839236348</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" si="1"/>
-        <v>17049.846983390125</v>
+        <f t="shared" si="2"/>
+        <v>17967.31876021075</v>
       </c>
     </row>
     <row r="5" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="9">
+        <f t="shared" ref="C5" si="3">C3+C4</f>
+        <v>8376</v>
+      </c>
+      <c r="D5" s="9">
+        <f t="shared" ref="D5" si="4">D3+D4</f>
+        <v>8953</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" ref="G5" si="5">G3+G4</f>
+        <v>8864</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" ref="H5:I5" si="6">H3+H4</f>
+        <v>9146</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="6"/>
+        <v>9212</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" ref="J5:K5" si="7">J3+J4</f>
+        <v>9440</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="7"/>
+        <v>9105</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" ref="L5:M5" si="8">L3+L4</f>
+        <v>9577</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="8"/>
+        <v>9728</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" ref="N5" si="9">N3+N4</f>
+        <v>10088</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" ref="O5:R5" si="10">O3+O4</f>
+        <v>9822</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" si="10"/>
+        <v>10352</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" si="10"/>
+        <v>10638.04</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" si="10"/>
+        <v>10957.82</v>
+      </c>
       <c r="T5" s="9">
-        <f t="shared" ref="T5:Z5" si="2">T3+T4</f>
+        <f t="shared" ref="T5:Z5" si="11">T3+T4</f>
         <v>36709</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>32637</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>34392</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>35466</v>
       </c>
       <c r="X5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>36662</v>
       </c>
       <c r="Y5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>38498</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" si="2"/>
-        <v>39738.31</v>
+        <f t="shared" si="11"/>
+        <v>41769.86</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" ref="AA5:AJ5" si="3">AA3+AA4</f>
-        <v>40663.553899999999</v>
+        <f t="shared" ref="AA5:AJ5" si="12">AA3+AA4</f>
+        <v>44276.051600000006</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="3"/>
-        <v>41485.879819000009</v>
+        <f t="shared" si="12"/>
+        <v>46489.854180000009</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="3"/>
-        <v>42188.950613990004</v>
+        <f t="shared" si="12"/>
+        <v>48349.448347200007</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="3"/>
-        <v>42759.269298481908</v>
+        <f t="shared" si="12"/>
+        <v>49799.931797616002</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="3"/>
-        <v>43338.259753385762</v>
+        <f t="shared" si="12"/>
+        <v>50953.926105132967</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="3"/>
-        <v>43926.068068077046</v>
+        <f t="shared" si="12"/>
+        <v>51626.20090789588</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="3"/>
-        <v>44522.842980258385</v>
+        <f t="shared" si="12"/>
+        <v>52308.453169520653</v>
       </c>
       <c r="AH5" s="9">
-        <f t="shared" si="3"/>
-        <v>45128.735926191555</v>
+        <f t="shared" si="12"/>
+        <v>53000.847758812582</v>
       </c>
       <c r="AI5" s="9">
-        <f t="shared" si="3"/>
-        <v>45743.901091906664</v>
+        <f t="shared" si="12"/>
+        <v>53703.552495149372</v>
       </c>
       <c r="AJ5" s="9">
-        <f t="shared" si="3"/>
-        <v>46368.495465407985</v>
+        <f t="shared" si="12"/>
+        <v>54416.738204024499</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C6" s="6">
+        <v>4059</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4329</v>
+      </c>
+      <c r="G6" s="6">
+        <v>4068</v>
+      </c>
+      <c r="H6" s="6">
+        <v>4133</v>
+      </c>
+      <c r="I6" s="6">
+        <v>4090</v>
+      </c>
+      <c r="J6" s="6">
+        <f t="shared" ref="J6:J7" si="13">X6-I6-H6-G6</f>
+        <v>4686</v>
+      </c>
+      <c r="K6" s="6">
+        <v>4035</v>
+      </c>
+      <c r="L6" s="6">
+        <v>4247</v>
+      </c>
+      <c r="M6" s="6">
+        <v>4166</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ref="N6:N7" si="14">Y6-M6-L6-K6</f>
+        <v>4779</v>
+      </c>
+      <c r="O6" s="6">
+        <v>4251</v>
+      </c>
+      <c r="P6" s="6">
+        <v>4548</v>
+      </c>
+      <c r="Q6" s="6">
+        <f>Q3*0.64</f>
+        <v>4639.3600000000006</v>
+      </c>
+      <c r="R6" s="6">
+        <f>R3*0.68</f>
+        <v>5103.3456000000006</v>
+      </c>
       <c r="T6" s="6">
         <v>19269</v>
       </c>
@@ -1155,54 +1399,100 @@
         <v>17227</v>
       </c>
       <c r="Z6" s="6">
-        <f>Z3*0.66</f>
-        <v>17517.581400000003</v>
+        <f t="shared" ref="Z6:Z7" si="15">SUM(O6:R6)</f>
+        <v>18541.705600000001</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" ref="AA6:AJ6" si="4">AA3*0.66</f>
-        <v>17692.757214000001</v>
+        <f t="shared" ref="AA6:AJ6" si="16">AA3*0.66</f>
+        <v>19951.136832</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="4"/>
-        <v>17869.684786140002</v>
+        <f t="shared" si="16"/>
+        <v>20948.693673600003</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="4"/>
-        <v>18048.381634001402</v>
+        <f t="shared" si="16"/>
+        <v>21786.641420544001</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="4"/>
-        <v>18228.865450341415</v>
+        <f t="shared" si="16"/>
+        <v>22440.240663160323</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="4"/>
-        <v>18411.154104844831</v>
+        <f t="shared" si="16"/>
+        <v>22889.045476423533</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="4"/>
-        <v>18595.26564589328</v>
+        <f t="shared" si="16"/>
+        <v>23117.935931187771</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="4"/>
-        <v>18781.218302352212</v>
+        <f t="shared" si="16"/>
+        <v>23349.115290499645</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="4"/>
-        <v>18969.030485375733</v>
+        <f t="shared" si="16"/>
+        <v>23582.606443404642</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="4"/>
-        <v>19158.720790229494</v>
+        <f t="shared" si="16"/>
+        <v>23818.432507838686</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="4"/>
-        <v>19350.30799813179</v>
+        <f t="shared" si="16"/>
+        <v>24056.616832917076</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C7" s="6">
+        <v>1265</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1331</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1430</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1493</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1580</v>
+      </c>
+      <c r="J7" s="6">
+        <f t="shared" si="13"/>
+        <v>1515</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1548</v>
+      </c>
+      <c r="L7" s="6">
+        <v>1609</v>
+      </c>
+      <c r="M7" s="6">
+        <v>1813</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" si="14"/>
+        <v>1639</v>
+      </c>
+      <c r="O7" s="6">
+        <v>1786</v>
+      </c>
+      <c r="P7" s="6">
+        <v>1781</v>
+      </c>
+      <c r="Q7" s="6">
+        <f>Q4*0.54</f>
+        <v>1830.0816000000004</v>
+      </c>
+      <c r="R7" s="6">
+        <f>R4*0.54</f>
+        <v>1864.5660000000003</v>
+      </c>
       <c r="T7" s="6">
         <v>5070</v>
       </c>
@@ -1222,199 +1512,357 @@
         <v>6609</v>
       </c>
       <c r="Z7" s="6">
-        <f>Z4*0.53</f>
-        <v>6994.155600000001</v>
+        <f t="shared" si="15"/>
+        <v>7261.6476000000002</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" ref="AA7:AJ7" si="5">AA4*0.53</f>
-        <v>7343.8633800000007</v>
+        <f t="shared" ref="AA7:AJ7" si="17">AA4*0.53</f>
+        <v>7444.9398920000012</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" si="5"/>
-        <v>7637.6179152000013</v>
+        <f t="shared" si="17"/>
+        <v>7817.1868866000013</v>
       </c>
       <c r="AC7" s="6">
-        <f t="shared" si="5"/>
-        <v>7866.7464526560025</v>
+        <f t="shared" si="17"/>
+        <v>8129.8743620640016</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="5"/>
-        <v>8024.081381709123</v>
+        <f t="shared" si="17"/>
+        <v>8373.7705929259209</v>
       </c>
       <c r="AE7" s="6">
-        <f t="shared" si="5"/>
-        <v>8184.5630093433047</v>
+        <f t="shared" si="17"/>
+        <v>8624.9837107136991</v>
       </c>
       <c r="AF7" s="6">
-        <f t="shared" si="5"/>
-        <v>8348.2542695301709</v>
+        <f t="shared" si="17"/>
+        <v>8797.483384927973</v>
       </c>
       <c r="AG7" s="6">
-        <f t="shared" si="5"/>
-        <v>8515.219354920775</v>
+        <f t="shared" si="17"/>
+        <v>8973.433052626533</v>
       </c>
       <c r="AH7" s="6">
-        <f t="shared" si="5"/>
-        <v>8685.5237420191916</v>
+        <f t="shared" si="17"/>
+        <v>9152.9017136790626</v>
       </c>
       <c r="AI7" s="6">
-        <f t="shared" si="5"/>
-        <v>8859.2342168595751</v>
+        <f t="shared" si="17"/>
+        <v>9335.9597479526437</v>
       </c>
       <c r="AJ7" s="6">
-        <f t="shared" si="5"/>
-        <v>9036.4189011967665</v>
+        <f t="shared" si="17"/>
+        <v>9522.678942911698</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="C8" s="6">
+        <f t="shared" ref="C8" si="18">C6+C7</f>
+        <v>5324</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="19">D6+D7</f>
+        <v>5660</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" ref="G8" si="20">G6+G7</f>
+        <v>5498</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" ref="H8:I8" si="21">H6+H7</f>
+        <v>5626</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="21"/>
+        <v>5670</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" ref="J8:K8" si="22">J6+J7</f>
+        <v>6201</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="22"/>
+        <v>5583</v>
+      </c>
+      <c r="L8" s="6">
+        <f t="shared" ref="L8:M8" si="23">L6+L7</f>
+        <v>5856</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" si="23"/>
+        <v>5979</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ref="N8" si="24">N6+N7</f>
+        <v>6418</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" ref="O8:P8" si="25">O6+O7</f>
+        <v>6037</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="25"/>
+        <v>6329</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" ref="Q8:R8" si="26">Q6+Q7</f>
+        <v>6469.441600000001</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="26"/>
+        <v>6967.9116000000013</v>
+      </c>
       <c r="T8" s="6">
-        <f t="shared" ref="T8:Y8" si="6">T6+T7</f>
+        <f t="shared" ref="T8:Y8" si="27">T6+T7</f>
         <v>24339</v>
       </c>
       <c r="U8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="27"/>
         <v>22169</v>
       </c>
       <c r="V8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="27"/>
         <v>23394</v>
       </c>
       <c r="W8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="27"/>
         <v>22347</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="27"/>
         <v>22995</v>
       </c>
       <c r="Y8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="27"/>
         <v>23836</v>
       </c>
       <c r="Z8" s="6">
-        <f t="shared" ref="Z8:AJ8" si="7">Z6+Z7</f>
-        <v>24511.737000000005</v>
+        <f t="shared" ref="Z8:AJ8" si="28">Z6+Z7</f>
+        <v>25803.353200000001</v>
       </c>
       <c r="AA8" s="6">
-        <f t="shared" si="7"/>
-        <v>25036.620594</v>
+        <f t="shared" si="28"/>
+        <v>27396.076724000002</v>
       </c>
       <c r="AB8" s="6">
-        <f t="shared" si="7"/>
-        <v>25507.302701340002</v>
+        <f t="shared" si="28"/>
+        <v>28765.880560200003</v>
       </c>
       <c r="AC8" s="6">
-        <f t="shared" si="7"/>
-        <v>25915.128086657405</v>
+        <f t="shared" si="28"/>
+        <v>29916.515782608003</v>
       </c>
       <c r="AD8" s="6">
-        <f t="shared" si="7"/>
-        <v>26252.946832050537</v>
+        <f t="shared" si="28"/>
+        <v>30814.011256086244</v>
       </c>
       <c r="AE8" s="6">
-        <f t="shared" si="7"/>
-        <v>26595.717114188134</v>
+        <f t="shared" si="28"/>
+        <v>31514.029187137232</v>
       </c>
       <c r="AF8" s="6">
-        <f t="shared" si="7"/>
-        <v>26943.519915423451</v>
+        <f t="shared" si="28"/>
+        <v>31915.419316115745</v>
       </c>
       <c r="AG8" s="6">
-        <f t="shared" si="7"/>
-        <v>27296.437657272989</v>
+        <f t="shared" si="28"/>
+        <v>32322.548343126178</v>
       </c>
       <c r="AH8" s="6">
-        <f t="shared" si="7"/>
-        <v>27654.554227394925</v>
+        <f t="shared" si="28"/>
+        <v>32735.508157083706</v>
       </c>
       <c r="AI8" s="6">
-        <f t="shared" si="7"/>
-        <v>28017.955007089069</v>
+        <f t="shared" si="28"/>
+        <v>33154.392255791332</v>
       </c>
       <c r="AJ8" s="6">
-        <f t="shared" si="7"/>
-        <v>28386.726899328554</v>
+        <f t="shared" si="28"/>
+        <v>33579.295775828774</v>
       </c>
     </row>
     <row r="9" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="C9" s="9">
+        <f t="shared" ref="C9" si="29">C5-C8</f>
+        <v>3052</v>
+      </c>
+      <c r="D9" s="9">
+        <f t="shared" ref="D9" si="30">D5-D8</f>
+        <v>3293</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" ref="G9" si="31">G5-G8</f>
+        <v>3366</v>
+      </c>
+      <c r="H9" s="9">
+        <f t="shared" ref="H9:I9" si="32">H5-H8</f>
+        <v>3520</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="32"/>
+        <v>3542</v>
+      </c>
+      <c r="J9" s="9">
+        <f t="shared" ref="J9:K9" si="33">J5-J8</f>
+        <v>3239</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="33"/>
+        <v>3522</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" ref="L9:M9" si="34">L5-L8</f>
+        <v>3721</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="34"/>
+        <v>3749</v>
+      </c>
+      <c r="N9" s="9">
+        <f t="shared" ref="N9" si="35">N5-N8</f>
+        <v>3670</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="shared" ref="O9:P9" si="36">O5-O8</f>
+        <v>3785</v>
+      </c>
+      <c r="P9" s="9">
+        <f t="shared" si="36"/>
+        <v>4023</v>
+      </c>
+      <c r="Q9" s="9">
+        <f t="shared" ref="Q9:R9" si="37">Q5-Q8</f>
+        <v>4168.5983999999999</v>
+      </c>
+      <c r="R9" s="9">
+        <f t="shared" si="37"/>
+        <v>3989.9083999999984</v>
+      </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9:Y9" si="8">T5-T8</f>
+        <f t="shared" ref="T9:Y9" si="38">T5-T8</f>
         <v>12370</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>10468</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>10998</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>13119</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>13667</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>14662</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" ref="Z9:AJ9" si="9">Z5-Z8</f>
-        <v>15226.572999999993</v>
+        <f t="shared" ref="Z9:AJ9" si="39">Z5-Z8</f>
+        <v>15966.506799999999</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="9"/>
-        <v>15626.933305999999</v>
+        <f t="shared" si="39"/>
+        <v>16879.974876000004</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="9"/>
-        <v>15978.577117660006</v>
+        <f t="shared" si="39"/>
+        <v>17723.973619800006</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="9"/>
-        <v>16273.822527332599</v>
+        <f t="shared" si="39"/>
+        <v>18432.932564592003</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" si="9"/>
-        <v>16506.322466431371</v>
+        <f t="shared" si="39"/>
+        <v>18985.920541529758</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="9"/>
-        <v>16742.542639197629</v>
+        <f t="shared" si="39"/>
+        <v>19439.896917995735</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" si="9"/>
-        <v>16982.548152653595</v>
+        <f t="shared" si="39"/>
+        <v>19710.781591780134</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" si="9"/>
-        <v>17226.405322985396</v>
+        <f t="shared" si="39"/>
+        <v>19985.904826394475</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" si="9"/>
-        <v>17474.18169879663</v>
+        <f t="shared" si="39"/>
+        <v>20265.339601728876</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="9"/>
-        <v>17725.946084817595</v>
+        <f t="shared" si="39"/>
+        <v>20549.16023935804</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" si="9"/>
-        <v>17981.76856607943</v>
+        <f t="shared" si="39"/>
+        <v>20837.442428195725</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="C10" s="6">
+        <v>350</v>
+      </c>
+      <c r="D10" s="6">
+        <v>386</v>
+      </c>
+      <c r="G10" s="6">
+        <v>357</v>
+      </c>
+      <c r="H10" s="6">
+        <v>375</v>
+      </c>
+      <c r="I10" s="6">
+        <v>364</v>
+      </c>
+      <c r="J10" s="6">
+        <f t="shared" ref="J10:J12" si="40">X10-I10-H10-G10</f>
+        <v>360</v>
+      </c>
+      <c r="K10" s="6">
+        <v>360</v>
+      </c>
+      <c r="L10" s="6">
+        <v>382</v>
+      </c>
+      <c r="M10" s="6">
+        <v>368</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" ref="N10:N12" si="41">Y10-M10-L10-K10</f>
+        <v>426</v>
+      </c>
+      <c r="O10" s="6">
+        <v>439</v>
+      </c>
+      <c r="P10" s="6">
+        <v>481</v>
+      </c>
+      <c r="Q10" s="6">
+        <f>M10*1.25</f>
+        <v>460</v>
+      </c>
+      <c r="R10" s="6">
+        <f>N10*1.2</f>
+        <v>511.2</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="6"/>
@@ -1429,54 +1877,100 @@
         <v>1536</v>
       </c>
       <c r="Z10" s="6">
-        <f>Y10*1.03</f>
-        <v>1582.08</v>
+        <f t="shared" ref="Z10:Z12" si="42">SUM(O10:R10)</f>
+        <v>1891.2</v>
       </c>
       <c r="AA10" s="6">
-        <f>Z10*1.02</f>
-        <v>1613.7215999999999</v>
+        <f>Z10*1.12</f>
+        <v>2118.1440000000002</v>
       </c>
       <c r="AB10" s="6">
-        <f t="shared" ref="AB10:AJ10" si="10">AA10*1.02</f>
-        <v>1645.9960319999998</v>
+        <f>AA10*1.07</f>
+        <v>2266.4140800000005</v>
       </c>
       <c r="AC10" s="6">
-        <f t="shared" si="10"/>
-        <v>1678.9159526399999</v>
+        <f>AB10*1.03</f>
+        <v>2334.4065024000006</v>
       </c>
       <c r="AD10" s="6">
-        <f t="shared" si="10"/>
-        <v>1712.4942716927999</v>
+        <f t="shared" ref="AD10:AJ10" si="43">AC10*1.02</f>
+        <v>2381.0946324480005</v>
       </c>
       <c r="AE10" s="6">
-        <f t="shared" si="10"/>
-        <v>1746.7441571266559</v>
+        <f t="shared" si="43"/>
+        <v>2428.7165250969606</v>
       </c>
       <c r="AF10" s="6">
-        <f t="shared" si="10"/>
-        <v>1781.679040269189</v>
+        <f t="shared" si="43"/>
+        <v>2477.2908555988997</v>
       </c>
       <c r="AG10" s="6">
-        <f t="shared" si="10"/>
-        <v>1817.3126210745729</v>
+        <f t="shared" si="43"/>
+        <v>2526.8366727108778</v>
       </c>
       <c r="AH10" s="6">
-        <f t="shared" si="10"/>
-        <v>1853.6588734960644</v>
+        <f t="shared" si="43"/>
+        <v>2577.3734061650953</v>
       </c>
       <c r="AI10" s="6">
-        <f t="shared" si="10"/>
-        <v>1890.7320509659858</v>
+        <f t="shared" si="43"/>
+        <v>2628.920874288397</v>
       </c>
       <c r="AJ10" s="6">
-        <f t="shared" si="10"/>
-        <v>1928.5466919853054</v>
+        <f t="shared" si="43"/>
+        <v>2681.4992917741652</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C11" s="6">
+        <v>1431</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1306</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1317</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1262</v>
+      </c>
+      <c r="I11" s="6">
+        <v>1252</v>
+      </c>
+      <c r="J11" s="6">
+        <f t="shared" si="40"/>
+        <v>1296</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1302</v>
+      </c>
+      <c r="L11" s="6">
+        <v>1361</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1398</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" si="41"/>
+        <v>1405</v>
+      </c>
+      <c r="O11" s="6">
+        <v>1361</v>
+      </c>
+      <c r="P11" s="6">
+        <v>1428</v>
+      </c>
+      <c r="Q11" s="6">
+        <f>M11*1.05</f>
+        <v>1467.9</v>
+      </c>
+      <c r="R11" s="6">
+        <f>N11*1.05</f>
+        <v>1475.25</v>
+      </c>
       <c r="T11" s="6">
         <v>5519</v>
       </c>
@@ -1496,54 +1990,98 @@
         <v>5466</v>
       </c>
       <c r="Z11" s="6">
-        <f>Y11*1.03</f>
-        <v>5629.9800000000005</v>
+        <f t="shared" si="42"/>
+        <v>5732.15</v>
       </c>
       <c r="AA11" s="6">
-        <f>Z11*1.02</f>
-        <v>5742.5796000000009</v>
+        <f>Z11*1.03</f>
+        <v>5904.1144999999997</v>
       </c>
       <c r="AB11" s="6">
-        <f>AA11*1.01</f>
-        <v>5800.0053960000014</v>
+        <f>AA11*1.02</f>
+        <v>6022.19679</v>
       </c>
       <c r="AC11" s="6">
-        <f t="shared" ref="AC11:AJ11" si="11">AB11*1.01</f>
-        <v>5858.0054499600019</v>
+        <f t="shared" ref="AC11:AJ11" si="44">AB11*1.01</f>
+        <v>6082.4187578999999</v>
       </c>
       <c r="AD11" s="6">
-        <f t="shared" si="11"/>
-        <v>5916.5855044596019</v>
+        <f t="shared" si="44"/>
+        <v>6143.2429454789999</v>
       </c>
       <c r="AE11" s="6">
-        <f t="shared" si="11"/>
-        <v>5975.7513595041983</v>
+        <f t="shared" si="44"/>
+        <v>6204.6753749337895</v>
       </c>
       <c r="AF11" s="6">
-        <f t="shared" si="11"/>
-        <v>6035.5088730992402</v>
+        <f t="shared" si="44"/>
+        <v>6266.7221286831273</v>
       </c>
       <c r="AG11" s="6">
-        <f t="shared" si="11"/>
-        <v>6095.8639618302323</v>
+        <f t="shared" si="44"/>
+        <v>6329.3893499699589</v>
       </c>
       <c r="AH11" s="6">
-        <f t="shared" si="11"/>
-        <v>6156.8226014485344</v>
+        <f t="shared" si="44"/>
+        <v>6392.6832434696589</v>
       </c>
       <c r="AI11" s="6">
-        <f t="shared" si="11"/>
-        <v>6218.3908274630203</v>
+        <f t="shared" si="44"/>
+        <v>6456.6100759043557</v>
       </c>
       <c r="AJ11" s="6">
-        <f t="shared" si="11"/>
-        <v>6280.5747357376504</v>
+        <f t="shared" si="44"/>
+        <v>6521.176176663399</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>125</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="41"/>
+        <v>94</v>
+      </c>
+      <c r="O12" s="6">
+        <v>15</v>
+      </c>
+      <c r="P12" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
@@ -1563,7 +2101,8 @@
         <v>219</v>
       </c>
       <c r="Z12" s="6">
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>15</v>
       </c>
       <c r="AA12" s="6">
         <v>0</v>
@@ -1600,152 +2139,310 @@
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C13" s="6">
+        <f t="shared" ref="C13" si="45">SUM(C10:C12)</f>
+        <v>1781</v>
+      </c>
+      <c r="D13" s="6">
+        <f t="shared" ref="D13" si="46">SUM(D10:D12)</f>
+        <v>1692</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" ref="G13" si="47">SUM(G10:G12)</f>
+        <v>1674</v>
+      </c>
+      <c r="H13" s="6">
+        <f t="shared" ref="H13:I13" si="48">SUM(H10:H12)</f>
+        <v>1637</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="48"/>
+        <v>1616</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" ref="J13:K13" si="49">SUM(J10:J12)</f>
+        <v>1656</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="49"/>
+        <v>1662</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" ref="L13" si="50">SUM(L10:L12)</f>
+        <v>1743</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" ref="M13:N13" si="51">SUM(M10:M12)</f>
+        <v>1891</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="51"/>
+        <v>1925</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" ref="O13:P13" si="52">SUM(O10:O12)</f>
+        <v>1815</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="52"/>
+        <v>1909</v>
+      </c>
+      <c r="Q13" s="6">
+        <f t="shared" ref="Q13:R13" si="53">SUM(Q10:Q12)</f>
+        <v>1927.9</v>
+      </c>
+      <c r="R13" s="6">
+        <f t="shared" si="53"/>
+        <v>1986.45</v>
+      </c>
       <c r="T13" s="6">
-        <f t="shared" ref="T13:Y13" si="12">SUM(T10:T12)</f>
+        <f t="shared" ref="T13:Y13" si="54">SUM(T10:T12)</f>
         <v>5519</v>
       </c>
       <c r="U13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="54"/>
         <v>4772</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="54"/>
         <v>4798</v>
       </c>
       <c r="W13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="54"/>
         <v>6692</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="54"/>
         <v>6583</v>
       </c>
       <c r="Y13" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="54"/>
         <v>7221</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" ref="Z13:AJ13" si="13">SUM(Z10:Z12)</f>
-        <v>7212.06</v>
+        <f t="shared" ref="Z13:AJ13" si="55">SUM(Z10:Z12)</f>
+        <v>7638.3499999999995</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="13"/>
-        <v>7356.3012000000008</v>
+        <f t="shared" si="55"/>
+        <v>8022.2584999999999</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="13"/>
-        <v>7446.0014280000014</v>
+        <f t="shared" si="55"/>
+        <v>8288.6108700000004</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="13"/>
-        <v>7536.9214026000018</v>
+        <f t="shared" si="55"/>
+        <v>8416.8252603000001</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" si="13"/>
-        <v>7629.0797761524018</v>
+        <f t="shared" si="55"/>
+        <v>8524.3375779270009</v>
       </c>
       <c r="AE13" s="6">
-        <f t="shared" si="13"/>
-        <v>7722.4955166308537</v>
+        <f t="shared" si="55"/>
+        <v>8633.3919000307505</v>
       </c>
       <c r="AF13" s="6">
-        <f t="shared" si="13"/>
-        <v>7817.1879133684288</v>
+        <f t="shared" si="55"/>
+        <v>8744.0129842820279</v>
       </c>
       <c r="AG13" s="6">
-        <f t="shared" si="13"/>
-        <v>7913.1765829048054</v>
+        <f t="shared" si="55"/>
+        <v>8856.2260226808357</v>
       </c>
       <c r="AH13" s="6">
-        <f t="shared" si="13"/>
-        <v>8010.4814749445986</v>
+        <f t="shared" si="55"/>
+        <v>8970.0566496347546</v>
       </c>
       <c r="AI13" s="6">
-        <f t="shared" si="13"/>
-        <v>8109.1228784290061</v>
+        <f t="shared" si="55"/>
+        <v>9085.5309501927532</v>
       </c>
       <c r="AJ13" s="6">
-        <f t="shared" si="13"/>
-        <v>8209.1214277229556</v>
+        <f t="shared" si="55"/>
+        <v>9202.6754684375646</v>
       </c>
     </row>
     <row r="14" spans="2:36" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C14" s="9">
+        <f t="shared" ref="C14" si="56">C9-C13</f>
+        <v>1271</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" ref="D14" si="57">D9-D13</f>
+        <v>1601</v>
+      </c>
+      <c r="G14" s="9">
+        <f t="shared" ref="G14" si="58">G9-G13</f>
+        <v>1692</v>
+      </c>
+      <c r="H14" s="9">
+        <f t="shared" ref="H14:I14" si="59">H9-H13</f>
+        <v>1883</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="59"/>
+        <v>1926</v>
+      </c>
+      <c r="J14" s="9">
+        <f t="shared" ref="J14:K14" si="60">J9-J13</f>
+        <v>1583</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" si="60"/>
+        <v>1860</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" ref="L14:M14" si="61">L9-L13</f>
+        <v>1978</v>
+      </c>
+      <c r="M14" s="9">
+        <f t="shared" si="61"/>
+        <v>1858</v>
+      </c>
+      <c r="N14" s="9">
+        <f t="shared" ref="N14" si="62">N9-N13</f>
+        <v>1745</v>
+      </c>
+      <c r="O14" s="9">
+        <f t="shared" ref="O14:P14" si="63">O9-O13</f>
+        <v>1970</v>
+      </c>
+      <c r="P14" s="9">
+        <f t="shared" si="63"/>
+        <v>2114</v>
+      </c>
+      <c r="Q14" s="9">
+        <f t="shared" ref="Q14:R14" si="64">Q9-Q13</f>
+        <v>2240.6983999999998</v>
+      </c>
+      <c r="R14" s="9">
+        <f t="shared" si="64"/>
+        <v>2003.4583999999984</v>
+      </c>
       <c r="T14" s="9">
-        <f t="shared" ref="T14:Y14" si="14">T9-T13</f>
+        <f t="shared" ref="T14:Y14" si="65">T9-T13</f>
         <v>6851</v>
       </c>
       <c r="U14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="65"/>
         <v>5696</v>
       </c>
       <c r="V14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="65"/>
         <v>6200</v>
       </c>
       <c r="W14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="65"/>
         <v>6427</v>
       </c>
       <c r="X14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="65"/>
         <v>7084</v>
       </c>
       <c r="Y14" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="65"/>
         <v>7441</v>
       </c>
       <c r="Z14" s="9">
-        <f t="shared" ref="Z14:AJ14" si="15">Z9-Z13</f>
-        <v>8014.5129999999926</v>
+        <f t="shared" ref="Z14:AJ14" si="66">Z9-Z13</f>
+        <v>8328.1568000000007</v>
       </c>
       <c r="AA14" s="9">
-        <f t="shared" si="15"/>
-        <v>8270.6321059999973</v>
+        <f t="shared" si="66"/>
+        <v>8857.7163760000039</v>
       </c>
       <c r="AB14" s="9">
-        <f t="shared" si="15"/>
-        <v>8532.5756896600051</v>
+        <f t="shared" si="66"/>
+        <v>9435.362749800006</v>
       </c>
       <c r="AC14" s="9">
-        <f t="shared" si="15"/>
-        <v>8736.901124732598</v>
+        <f t="shared" si="66"/>
+        <v>10016.107304292003</v>
       </c>
       <c r="AD14" s="9">
-        <f t="shared" si="15"/>
-        <v>8877.2426902789703</v>
+        <f t="shared" si="66"/>
+        <v>10461.582963602757</v>
       </c>
       <c r="AE14" s="9">
-        <f t="shared" si="15"/>
-        <v>9020.0471225667752</v>
+        <f t="shared" si="66"/>
+        <v>10806.505017964984</v>
       </c>
       <c r="AF14" s="9">
-        <f t="shared" si="15"/>
-        <v>9165.3602392851662</v>
+        <f t="shared" si="66"/>
+        <v>10966.768607498107</v>
       </c>
       <c r="AG14" s="9">
-        <f t="shared" si="15"/>
-        <v>9313.2287400805908</v>
+        <f t="shared" si="66"/>
+        <v>11129.678803713639</v>
       </c>
       <c r="AH14" s="9">
-        <f t="shared" si="15"/>
-        <v>9463.7002238520327</v>
+        <f t="shared" si="66"/>
+        <v>11295.282952094121</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="15"/>
-        <v>9616.823206388588</v>
+        <f t="shared" si="66"/>
+        <v>11463.629289165287</v>
       </c>
       <c r="AJ14" s="9">
-        <f t="shared" si="15"/>
-        <v>9772.6471383564749</v>
+        <f t="shared" si="66"/>
+        <v>11634.766959758161</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C15" s="6">
+        <v>-319</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-190</v>
+      </c>
+      <c r="G15" s="6">
+        <v>-260</v>
+      </c>
+      <c r="H15" s="6">
+        <v>-208</v>
+      </c>
+      <c r="I15" s="6">
+        <v>-247</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" ref="J15:J16" si="67">X15-I15-H15-G15</f>
+        <v>-125</v>
+      </c>
+      <c r="K15" s="6">
+        <v>-231</v>
+      </c>
+      <c r="L15" s="6">
+        <v>-246</v>
+      </c>
+      <c r="M15" s="6">
+        <v>-263</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" ref="N15:N16" si="68">Y15-M15-L15-K15</f>
+        <v>-90</v>
+      </c>
+      <c r="O15" s="6">
+        <v>-200</v>
+      </c>
+      <c r="P15" s="6">
+        <v>-87</v>
+      </c>
+      <c r="Q15" s="6">
+        <f>M15*1.01</f>
+        <v>-265.63</v>
+      </c>
+      <c r="R15" s="6">
+        <f>N15*1.01</f>
+        <v>-90.9</v>
+      </c>
       <c r="T15" s="6">
         <v>-1065</v>
       </c>
@@ -1765,54 +2462,100 @@
         <v>-830</v>
       </c>
       <c r="Z15" s="6">
-        <f>Y15*1.01</f>
-        <v>-838.3</v>
+        <f t="shared" ref="Z15:Z16" si="69">SUM(O15:R15)</f>
+        <v>-643.53</v>
       </c>
       <c r="AA15" s="6">
-        <f t="shared" ref="AA15:AJ15" si="16">Z15*1.01</f>
-        <v>-846.68299999999999</v>
+        <f t="shared" ref="AA15:AJ15" si="70">Z15*1.01</f>
+        <v>-649.96529999999996</v>
       </c>
       <c r="AB15" s="6">
-        <f t="shared" si="16"/>
-        <v>-855.14982999999995</v>
+        <f t="shared" si="70"/>
+        <v>-656.46495299999992</v>
       </c>
       <c r="AC15" s="6">
-        <f t="shared" si="16"/>
-        <v>-863.7013283</v>
+        <f t="shared" si="70"/>
+        <v>-663.02960252999992</v>
       </c>
       <c r="AD15" s="6">
-        <f t="shared" si="16"/>
-        <v>-872.33834158299999</v>
+        <f t="shared" si="70"/>
+        <v>-669.65989855529995</v>
       </c>
       <c r="AE15" s="6">
-        <f t="shared" si="16"/>
-        <v>-881.06172499882996</v>
+        <f t="shared" si="70"/>
+        <v>-676.35649754085296</v>
       </c>
       <c r="AF15" s="6">
-        <f t="shared" si="16"/>
-        <v>-889.87234224881831</v>
+        <f t="shared" si="70"/>
+        <v>-683.12006251626144</v>
       </c>
       <c r="AG15" s="6">
-        <f t="shared" si="16"/>
-        <v>-898.77106567130647</v>
+        <f t="shared" si="70"/>
+        <v>-689.95126314142408</v>
       </c>
       <c r="AH15" s="6">
-        <f t="shared" si="16"/>
-        <v>-907.75877632801951</v>
+        <f t="shared" si="70"/>
+        <v>-696.85077577283835</v>
       </c>
       <c r="AI15" s="6">
-        <f t="shared" si="16"/>
-        <v>-916.83636409129974</v>
+        <f t="shared" si="70"/>
+        <v>-703.81928353056674</v>
       </c>
       <c r="AJ15" s="6">
-        <f t="shared" si="16"/>
-        <v>-926.0047277322127</v>
+        <f t="shared" si="70"/>
+        <v>-710.85747636587246</v>
       </c>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="C16" s="6">
+        <v>85</v>
+      </c>
+      <c r="D16" s="6">
+        <v>87</v>
+      </c>
+      <c r="G16" s="6">
+        <v>170</v>
+      </c>
+      <c r="H16" s="6">
+        <v>187</v>
+      </c>
+      <c r="I16" s="6">
+        <v>206</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="67"/>
+        <v>202</v>
+      </c>
+      <c r="K16" s="6">
+        <v>220</v>
+      </c>
+      <c r="L16" s="6">
+        <v>250</v>
+      </c>
+      <c r="M16" s="6">
+        <v>297</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="68"/>
+        <v>291</v>
+      </c>
+      <c r="O16" s="6">
+        <v>286</v>
+      </c>
+      <c r="P16" s="6">
+        <v>330</v>
+      </c>
+      <c r="Q16" s="6">
+        <f>P16*1.01</f>
+        <v>333.3</v>
+      </c>
+      <c r="R16" s="6">
+        <f>Q16*1.01</f>
+        <v>336.63300000000004</v>
+      </c>
       <c r="T16" s="6">
         <v>357</v>
       </c>
@@ -1832,200 +2575,358 @@
         <v>1058</v>
       </c>
       <c r="Z16" s="6">
-        <f>Y16*1.02</f>
-        <v>1079.1600000000001</v>
+        <f t="shared" si="69"/>
+        <v>1285.933</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" ref="AA16:AJ16" si="17">Z16*1.02</f>
-        <v>1100.7432000000001</v>
+        <f t="shared" ref="AA16:AJ16" si="71">Z16*1.02</f>
+        <v>1311.65166</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="17"/>
-        <v>1122.7580640000001</v>
+        <f t="shared" si="71"/>
+        <v>1337.8846932000001</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="17"/>
-        <v>1145.2132252800002</v>
+        <f t="shared" si="71"/>
+        <v>1364.6423870640001</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="17"/>
-        <v>1168.1174897856001</v>
+        <f t="shared" si="71"/>
+        <v>1391.9352348052801</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="17"/>
-        <v>1191.4798395813123</v>
+        <f t="shared" si="71"/>
+        <v>1419.7739395013857</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="17"/>
-        <v>1215.3094363729385</v>
+        <f t="shared" si="71"/>
+        <v>1448.1694182914134</v>
       </c>
       <c r="AG16" s="6">
-        <f t="shared" si="17"/>
-        <v>1239.6156251003974</v>
+        <f t="shared" si="71"/>
+        <v>1477.1328066572416</v>
       </c>
       <c r="AH16" s="6">
-        <f t="shared" si="17"/>
-        <v>1264.4079376024054</v>
+        <f t="shared" si="71"/>
+        <v>1506.6754627903865</v>
       </c>
       <c r="AI16" s="6">
-        <f t="shared" si="17"/>
-        <v>1289.6960963544534</v>
+        <f t="shared" si="71"/>
+        <v>1536.8089720461942</v>
       </c>
       <c r="AJ16" s="6">
-        <f t="shared" si="17"/>
-        <v>1315.4900182815425</v>
+        <f t="shared" si="71"/>
+        <v>1567.5451514871181</v>
       </c>
     </row>
     <row r="17" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="C17" s="6">
+        <f t="shared" ref="C17" si="72">SUM(C15:C16)</f>
+        <v>-234</v>
+      </c>
+      <c r="D17" s="6">
+        <f t="shared" ref="D17" si="73">SUM(D15:D16)</f>
+        <v>-103</v>
+      </c>
+      <c r="G17" s="6">
+        <f t="shared" ref="G17" si="74">SUM(G15:G16)</f>
+        <v>-90</v>
+      </c>
+      <c r="H17" s="6">
+        <f t="shared" ref="H17:I17" si="75">SUM(H15:H16)</f>
+        <v>-21</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="75"/>
+        <v>-41</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" ref="J17:K17" si="76">SUM(J15:J16)</f>
+        <v>77</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="76"/>
+        <v>-11</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" ref="L17" si="77">SUM(L15:L16)</f>
+        <v>4</v>
+      </c>
+      <c r="M17" s="6">
+        <f t="shared" ref="M17:N17" si="78">SUM(M15:M16)</f>
+        <v>34</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="78"/>
+        <v>201</v>
+      </c>
+      <c r="O17" s="6">
+        <f t="shared" ref="O17:P17" si="79">SUM(O15:O16)</f>
+        <v>86</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="79"/>
+        <v>243</v>
+      </c>
+      <c r="Q17" s="6">
+        <f t="shared" ref="Q17:R17" si="80">SUM(Q15:Q16)</f>
+        <v>67.670000000000016</v>
+      </c>
+      <c r="R17" s="6">
+        <f t="shared" si="80"/>
+        <v>245.73300000000003</v>
+      </c>
       <c r="T17" s="6">
-        <f t="shared" ref="T17:Y17" si="18">SUM(T15:T16)</f>
+        <f t="shared" ref="T17:Y17" si="81">SUM(T15:T16)</f>
         <v>-708</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="81"/>
         <v>-316</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="81"/>
         <v>-1035</v>
       </c>
       <c r="W17" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="81"/>
         <v>48</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="81"/>
         <v>-75</v>
       </c>
       <c r="Y17" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="81"/>
         <v>228</v>
       </c>
       <c r="Z17" s="6">
-        <f t="shared" ref="Z17:AJ17" si="19">SUM(Z15:Z16)</f>
-        <v>240.86000000000013</v>
+        <f t="shared" ref="Z17:AJ17" si="82">SUM(Z15:Z16)</f>
+        <v>642.40300000000002</v>
       </c>
       <c r="AA17" s="6">
-        <f t="shared" si="19"/>
-        <v>254.06020000000012</v>
+        <f t="shared" si="82"/>
+        <v>661.68636000000004</v>
       </c>
       <c r="AB17" s="6">
-        <f t="shared" si="19"/>
-        <v>267.60823400000015</v>
+        <f t="shared" si="82"/>
+        <v>681.41974020000021</v>
       </c>
       <c r="AC17" s="6">
-        <f t="shared" si="19"/>
-        <v>281.51189698000019</v>
+        <f t="shared" si="82"/>
+        <v>701.61278453400018</v>
       </c>
       <c r="AD17" s="6">
-        <f t="shared" si="19"/>
-        <v>295.77914820260014</v>
+        <f t="shared" si="82"/>
+        <v>722.27533624998011</v>
       </c>
       <c r="AE17" s="6">
-        <f t="shared" si="19"/>
-        <v>310.4181145824823</v>
+        <f t="shared" si="82"/>
+        <v>743.41744196053276</v>
       </c>
       <c r="AF17" s="6">
-        <f t="shared" si="19"/>
-        <v>325.43709412412022</v>
+        <f t="shared" si="82"/>
+        <v>765.04935577515198</v>
       </c>
       <c r="AG17" s="6">
-        <f t="shared" si="19"/>
-        <v>340.84455942909096</v>
+        <f t="shared" si="82"/>
+        <v>787.18154351581757</v>
       </c>
       <c r="AH17" s="6">
-        <f t="shared" si="19"/>
-        <v>356.64916127438585</v>
+        <f t="shared" si="82"/>
+        <v>809.82468701754817</v>
       </c>
       <c r="AI17" s="6">
-        <f t="shared" si="19"/>
-        <v>372.85973226315366</v>
+        <f t="shared" si="82"/>
+        <v>832.98968851562745</v>
       </c>
       <c r="AJ17" s="6">
-        <f t="shared" si="19"/>
-        <v>389.48529054932976</v>
+        <f t="shared" si="82"/>
+        <v>856.68767512124566</v>
       </c>
     </row>
     <row r="18" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C18" s="9">
+        <f t="shared" ref="C18" si="83">C14-C17</f>
+        <v>1505</v>
+      </c>
+      <c r="D18" s="9">
+        <f t="shared" ref="D18" si="84">D14-D17</f>
+        <v>1704</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" ref="G18" si="85">G14-G17</f>
+        <v>1782</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" ref="H18:I18" si="86">H14-H17</f>
+        <v>1904</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="86"/>
+        <v>1967</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" ref="J18:K18" si="87">J14-J17</f>
+        <v>1506</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="87"/>
+        <v>1871</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" ref="L18:M18" si="88">L14-L17</f>
+        <v>1974</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="88"/>
+        <v>1824</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" ref="N18" si="89">N14-N17</f>
+        <v>1544</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" ref="O18:P18" si="90">O14-O17</f>
+        <v>1884</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="90"/>
+        <v>1871</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" ref="Q18:R18" si="91">Q14-Q17</f>
+        <v>2173.0283999999997</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="91"/>
+        <v>1757.7253999999984</v>
+      </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18:Y18" si="20">T14-T17</f>
+        <f t="shared" ref="T18:Y18" si="92">T14-T17</f>
         <v>7559</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="92"/>
         <v>6012</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="92"/>
         <v>7235</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="92"/>
         <v>6379</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="92"/>
         <v>7159</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="92"/>
         <v>7213</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AJ18" si="21">Z14-Z17</f>
-        <v>7773.652999999993</v>
+        <f t="shared" ref="Z18:AJ18" si="93">Z14-Z17</f>
+        <v>7685.7538000000004</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="21"/>
-        <v>8016.5719059999974</v>
+        <f t="shared" si="93"/>
+        <v>8196.0300160000043</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="21"/>
-        <v>8264.9674556600057</v>
+        <f t="shared" si="93"/>
+        <v>8753.9430096000051</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="21"/>
-        <v>8455.3892277525974</v>
+        <f t="shared" si="93"/>
+        <v>9314.4945197580037</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="21"/>
-        <v>8581.4635420763698</v>
+        <f t="shared" si="93"/>
+        <v>9739.3076273527768</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="21"/>
-        <v>8709.6290079842929</v>
+        <f t="shared" si="93"/>
+        <v>10063.087576004451</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="21"/>
-        <v>8839.9231451610467</v>
+        <f t="shared" si="93"/>
+        <v>10201.719251722954</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="21"/>
-        <v>8972.3841806514993</v>
+        <f t="shared" si="93"/>
+        <v>10342.497260197822</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="21"/>
-        <v>9107.051062577646</v>
+        <f t="shared" si="93"/>
+        <v>10485.458265076573</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="21"/>
-        <v>9243.963474125434</v>
+        <f t="shared" si="93"/>
+        <v>10630.63960064966</v>
       </c>
       <c r="AJ18" s="9">
-        <f t="shared" si="21"/>
-        <v>9383.161847807145</v>
+        <f t="shared" si="93"/>
+        <v>10778.079284636915</v>
       </c>
     </row>
     <row r="19" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="C19" s="6">
+        <v>371</v>
+      </c>
+      <c r="D19" s="6">
+        <v>441</v>
+      </c>
+      <c r="G19" s="6">
+        <v>374</v>
+      </c>
+      <c r="H19" s="6">
+        <v>403</v>
+      </c>
+      <c r="I19" s="6">
+        <v>452</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" ref="J19:J20" si="94">X19-I19-H19-G19</f>
+        <v>258</v>
+      </c>
+      <c r="K19" s="6">
+        <v>396</v>
+      </c>
+      <c r="L19" s="6">
+        <v>414</v>
+      </c>
+      <c r="M19" s="6">
+        <v>409</v>
+      </c>
+      <c r="N19" s="6">
+        <f t="shared" ref="N19:N20" si="95">Y19-M19-L19-K19</f>
+        <v>254</v>
+      </c>
+      <c r="O19" s="6">
+        <v>417</v>
+      </c>
+      <c r="P19" s="6">
+        <v>302</v>
+      </c>
+      <c r="Q19" s="6">
+        <f>Q18*0.18</f>
+        <v>391.14511199999993</v>
+      </c>
+      <c r="R19" s="6">
+        <f>R18*0.18</f>
+        <v>316.39057199999974</v>
+      </c>
       <c r="T19" s="6">
         <v>1329</v>
       </c>
@@ -2045,54 +2946,98 @@
         <v>1473</v>
       </c>
       <c r="Z19" s="6">
-        <f>Z18*0.21</f>
-        <v>1632.4671299999984</v>
+        <f t="shared" ref="Z19:Z20" si="96">SUM(O19:R19)</f>
+        <v>1426.5356839999997</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" ref="AA19:AJ19" si="22">AA18*0.21</f>
-        <v>1683.4801002599993</v>
+        <f t="shared" ref="AA19:AJ19" si="97">AA18*0.21</f>
+        <v>1721.1663033600009</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="22"/>
-        <v>1735.6431656886011</v>
+        <f t="shared" si="97"/>
+        <v>1838.3280320160011</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="22"/>
-        <v>1775.6317378280453</v>
+        <f t="shared" si="97"/>
+        <v>1956.0438491491807</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="22"/>
-        <v>1802.1073438360377</v>
+        <f t="shared" si="97"/>
+        <v>2045.2546017440829</v>
       </c>
       <c r="AE19" s="6">
-        <f t="shared" si="22"/>
-        <v>1829.0220916767014</v>
+        <f t="shared" si="97"/>
+        <v>2113.2483909609346</v>
       </c>
       <c r="AF19" s="6">
-        <f t="shared" si="22"/>
-        <v>1856.3838604838197</v>
+        <f t="shared" si="97"/>
+        <v>2142.3610428618204</v>
       </c>
       <c r="AG19" s="6">
-        <f t="shared" si="22"/>
-        <v>1884.2006779368148</v>
+        <f t="shared" si="97"/>
+        <v>2171.9244246415428</v>
       </c>
       <c r="AH19" s="6">
-        <f t="shared" si="22"/>
-        <v>1912.4807231413056</v>
+        <f t="shared" si="97"/>
+        <v>2201.9462356660802</v>
       </c>
       <c r="AI19" s="6">
-        <f t="shared" si="22"/>
-        <v>1941.2323295663411</v>
+        <f t="shared" si="97"/>
+        <v>2232.4343161364286</v>
       </c>
       <c r="AJ19" s="6">
-        <f t="shared" si="22"/>
-        <v>1970.4639880395005</v>
+        <f t="shared" si="97"/>
+        <v>2263.396649773752</v>
       </c>
     </row>
     <row r="20" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="G20" s="6">
+        <v>14</v>
+      </c>
+      <c r="H20" s="6">
+        <v>14</v>
+      </c>
+      <c r="I20" s="6">
+        <v>1</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="94"/>
+        <v>-15</v>
+      </c>
+      <c r="K20" s="6">
+        <v>12</v>
+      </c>
+      <c r="L20" s="6">
+        <v>16</v>
+      </c>
+      <c r="M20" s="6">
+        <v>2</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="95"/>
+        <v>5</v>
+      </c>
+      <c r="O20" s="6">
+        <v>18</v>
+      </c>
+      <c r="P20" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
       <c r="T20" s="6">
         <v>87</v>
       </c>
@@ -2112,7 +3057,8 @@
         <v>35</v>
       </c>
       <c r="Z20" s="6">
-        <v>0</v>
+        <f t="shared" si="96"/>
+        <v>17</v>
       </c>
       <c r="AA20" s="6">
         <v>0</v>
@@ -2149,688 +3095,900 @@
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="C21" s="9">
+        <f t="shared" ref="C21" si="98">C18-C19-C20</f>
+        <v>1134</v>
+      </c>
+      <c r="D21" s="9">
+        <f t="shared" ref="D21" si="99">D18-D19-D20</f>
+        <v>1261</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" ref="G21" si="100">G18-G19-G20</f>
+        <v>1394</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" ref="H21:I21" si="101">H18-H19-H20</f>
+        <v>1487</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="101"/>
+        <v>1514</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" ref="J21:K21" si="102">J18-J19-J20</f>
+        <v>1263</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" si="102"/>
+        <v>1463</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" ref="L21:M21" si="103">L18-L19-L20</f>
+        <v>1544</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="103"/>
+        <v>1413</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" ref="N21" si="104">N18-N19-N20</f>
+        <v>1285</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21:P21" si="105">O18-O19-O20</f>
+        <v>1449</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="105"/>
+        <v>1570</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" ref="Q21:R21" si="106">Q18-Q19-Q20</f>
+        <v>1781.8832879999998</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="106"/>
+        <v>1441.3348279999987</v>
+      </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21:Y21" si="23">T18-T19-T20</f>
+        <f t="shared" ref="T21:Y21" si="107">T18-T19-T20</f>
         <v>6143</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="107"/>
         <v>4779</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="107"/>
         <v>5542</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="107"/>
         <v>4966</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="107"/>
         <v>5658</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="107"/>
         <v>5705</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AJ21" si="24">Z18-Z19-Z20</f>
-        <v>6141.1858699999948</v>
+        <f t="shared" ref="Z21:AJ21" si="108">Z18-Z19-Z20</f>
+        <v>6242.2181160000009</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="24"/>
-        <v>6333.0918057399977</v>
+        <f t="shared" si="108"/>
+        <v>6474.8637126400035</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="24"/>
-        <v>6529.3242899714041</v>
+        <f t="shared" si="108"/>
+        <v>6915.614977584004</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="24"/>
-        <v>6679.7574899245519</v>
+        <f t="shared" si="108"/>
+        <v>7358.4506706088232</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="24"/>
-        <v>6779.3561982403317</v>
+        <f t="shared" si="108"/>
+        <v>7694.053025608694</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="24"/>
-        <v>6880.6069163075917</v>
+        <f t="shared" si="108"/>
+        <v>7949.8391850435164</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="24"/>
-        <v>6983.5392846772265</v>
+        <f t="shared" si="108"/>
+        <v>8059.3582088611338</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="24"/>
-        <v>7088.1835027146844</v>
+        <f t="shared" si="108"/>
+        <v>8170.5728355562796</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="24"/>
-        <v>7194.5703394363409</v>
+        <f t="shared" si="108"/>
+        <v>8283.5120294104927</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="24"/>
-        <v>7302.7311445590931</v>
+        <f t="shared" si="108"/>
+        <v>8398.2052845132312</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="24"/>
-        <v>7412.6978597676443</v>
+        <f t="shared" si="108"/>
+        <v>8514.6826348631621</v>
       </c>
       <c r="AK21" s="2">
         <f>AJ21*(1+$AM$26)</f>
-        <v>7338.5708811699678</v>
+        <v>8429.5358085145308</v>
       </c>
       <c r="AL21" s="2">
-        <f t="shared" ref="AL21:CW21" si="25">AK21*(1+$AM$26)</f>
-        <v>7265.1851723582677</v>
+        <f t="shared" ref="AL21:CW21" si="109">AK21*(1+$AM$26)</f>
+        <v>8345.2404504293845</v>
       </c>
       <c r="AM21" s="2">
-        <f t="shared" si="25"/>
-        <v>7192.533320634685</v>
+        <f t="shared" si="109"/>
+        <v>8261.78804592509</v>
       </c>
       <c r="AN21" s="2">
-        <f t="shared" si="25"/>
-        <v>7120.6079874283378</v>
+        <f t="shared" si="109"/>
+        <v>8179.1701654658391</v>
       </c>
       <c r="AO21" s="2">
-        <f t="shared" si="25"/>
-        <v>7049.4019075540546</v>
+        <f t="shared" si="109"/>
+        <v>8097.3784638111811</v>
       </c>
       <c r="AP21" s="2">
-        <f t="shared" si="25"/>
-        <v>6978.907888478514</v>
+        <f t="shared" si="109"/>
+        <v>8016.4046791730689</v>
       </c>
       <c r="AQ21" s="2">
-        <f t="shared" si="25"/>
-        <v>6909.1188095937287</v>
+        <f t="shared" si="109"/>
+        <v>7936.2406323813384</v>
       </c>
       <c r="AR21" s="2">
-        <f t="shared" si="25"/>
-        <v>6840.0276214977912</v>
+        <f t="shared" si="109"/>
+        <v>7856.8782260575254</v>
       </c>
       <c r="AS21" s="2">
-        <f t="shared" si="25"/>
-        <v>6771.6273452828136</v>
+        <f t="shared" si="109"/>
+        <v>7778.3094437969503</v>
       </c>
       <c r="AT21" s="2">
-        <f t="shared" si="25"/>
-        <v>6703.9110718299853</v>
+        <f t="shared" si="109"/>
+        <v>7700.526349358981</v>
       </c>
       <c r="AU21" s="2">
-        <f t="shared" si="25"/>
-        <v>6636.8719611116858</v>
+        <f t="shared" si="109"/>
+        <v>7623.5210858653909</v>
       </c>
       <c r="AV21" s="2">
-        <f t="shared" si="25"/>
-        <v>6570.5032415005689</v>
+        <f t="shared" si="109"/>
+        <v>7547.2858750067371</v>
       </c>
       <c r="AW21" s="2">
-        <f t="shared" si="25"/>
-        <v>6504.798209085563</v>
+        <f t="shared" si="109"/>
+        <v>7471.8130162566695</v>
       </c>
       <c r="AX21" s="2">
-        <f t="shared" si="25"/>
-        <v>6439.7502269947072</v>
+        <f t="shared" si="109"/>
+        <v>7397.0948860941025</v>
       </c>
       <c r="AY21" s="2">
-        <f t="shared" si="25"/>
-        <v>6375.3527247247603</v>
+        <f t="shared" si="109"/>
+        <v>7323.1239372331611</v>
       </c>
       <c r="AZ21" s="2">
-        <f t="shared" si="25"/>
-        <v>6311.5991974775125</v>
+        <f t="shared" si="109"/>
+        <v>7249.8926978608297</v>
       </c>
       <c r="BA21" s="2">
-        <f t="shared" si="25"/>
-        <v>6248.4832055027373</v>
+        <f t="shared" si="109"/>
+        <v>7177.3937708822214</v>
       </c>
       <c r="BB21" s="2">
-        <f t="shared" si="25"/>
-        <v>6185.99837344771</v>
+        <f t="shared" si="109"/>
+        <v>7105.6198331733995</v>
       </c>
       <c r="BC21" s="2">
-        <f t="shared" si="25"/>
-        <v>6124.1383897132328</v>
+        <f t="shared" si="109"/>
+        <v>7034.5636348416656</v>
       </c>
       <c r="BD21" s="2">
-        <f t="shared" si="25"/>
-        <v>6062.8970058161003</v>
+        <f t="shared" si="109"/>
+        <v>6964.2179984932491</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" si="25"/>
-        <v>6002.2680357579393</v>
+        <f t="shared" si="109"/>
+        <v>6894.5758185083168</v>
       </c>
       <c r="BF21" s="2">
-        <f t="shared" si="25"/>
-        <v>5942.2453554003596</v>
+        <f t="shared" si="109"/>
+        <v>6825.6300603232339</v>
       </c>
       <c r="BG21" s="2">
-        <f t="shared" si="25"/>
-        <v>5882.8229018463562</v>
+        <f t="shared" si="109"/>
+        <v>6757.3737597200015</v>
       </c>
       <c r="BH21" s="2">
-        <f t="shared" si="25"/>
-        <v>5823.9946728278928</v>
+        <f t="shared" si="109"/>
+        <v>6689.8000221228012</v>
       </c>
       <c r="BI21" s="2">
-        <f t="shared" si="25"/>
-        <v>5765.7547260996134</v>
+        <f t="shared" si="109"/>
+        <v>6622.9020219015729</v>
       </c>
       <c r="BJ21" s="2">
-        <f t="shared" si="25"/>
-        <v>5708.0971788386169</v>
+        <f t="shared" si="109"/>
+        <v>6556.6730016825568</v>
       </c>
       <c r="BK21" s="2">
-        <f t="shared" si="25"/>
-        <v>5651.0162070502311</v>
+        <f t="shared" si="109"/>
+        <v>6491.1062716657316</v>
       </c>
       <c r="BL21" s="2">
-        <f t="shared" si="25"/>
-        <v>5594.5060449797284</v>
+        <f t="shared" si="109"/>
+        <v>6426.1952089490742</v>
       </c>
       <c r="BM21" s="2">
-        <f t="shared" si="25"/>
-        <v>5538.5609845299314</v>
+        <f t="shared" si="109"/>
+        <v>6361.9332568595837</v>
       </c>
       <c r="BN21" s="2">
-        <f t="shared" si="25"/>
-        <v>5483.1753746846316</v>
+        <f t="shared" si="109"/>
+        <v>6298.3139242909874</v>
       </c>
       <c r="BO21" s="2">
-        <f t="shared" si="25"/>
-        <v>5428.3436209377851</v>
+        <f t="shared" si="109"/>
+        <v>6235.3307850480778</v>
       </c>
       <c r="BP21" s="2">
-        <f t="shared" si="25"/>
-        <v>5374.060184728407</v>
+        <f t="shared" si="109"/>
+        <v>6172.9774771975972</v>
       </c>
       <c r="BQ21" s="2">
-        <f t="shared" si="25"/>
-        <v>5320.3195828811231</v>
+        <f t="shared" si="109"/>
+        <v>6111.2477024256214</v>
       </c>
       <c r="BR21" s="2">
-        <f t="shared" si="25"/>
-        <v>5267.1163870523114</v>
+        <f t="shared" si="109"/>
+        <v>6050.1352254013655</v>
       </c>
       <c r="BS21" s="2">
-        <f t="shared" si="25"/>
-        <v>5214.4452231817886</v>
+        <f t="shared" si="109"/>
+        <v>5989.6338731473516</v>
       </c>
       <c r="BT21" s="2">
-        <f t="shared" si="25"/>
-        <v>5162.3007709499707</v>
+        <f t="shared" si="109"/>
+        <v>5929.7375344158781</v>
       </c>
       <c r="BU21" s="2">
-        <f t="shared" si="25"/>
-        <v>5110.677763240471</v>
+        <f t="shared" si="109"/>
+        <v>5870.4401590717189</v>
       </c>
       <c r="BV21" s="2">
-        <f t="shared" si="25"/>
-        <v>5059.5709856080666</v>
+        <f t="shared" si="109"/>
+        <v>5811.7357574810012</v>
       </c>
       <c r="BW21" s="2">
-        <f t="shared" si="25"/>
-        <v>5008.9752757519855</v>
+        <f t="shared" si="109"/>
+        <v>5753.6183999061914</v>
       </c>
       <c r="BX21" s="2">
-        <f t="shared" si="25"/>
-        <v>4958.8855229944656</v>
+        <f t="shared" si="109"/>
+        <v>5696.0822159071295</v>
       </c>
       <c r="BY21" s="2">
-        <f t="shared" si="25"/>
-        <v>4909.2966677645209</v>
+        <f t="shared" si="109"/>
+        <v>5639.1213937480579</v>
       </c>
       <c r="BZ21" s="2">
-        <f t="shared" si="25"/>
-        <v>4860.2037010868753</v>
+        <f t="shared" si="109"/>
+        <v>5582.7301798105773</v>
       </c>
       <c r="CA21" s="2">
-        <f t="shared" si="25"/>
-        <v>4811.6016640760063</v>
+        <f t="shared" si="109"/>
+        <v>5526.9028780124718</v>
       </c>
       <c r="CB21" s="2">
-        <f t="shared" si="25"/>
-        <v>4763.4856474352464</v>
+        <f t="shared" si="109"/>
+        <v>5471.6338492323466</v>
       </c>
       <c r="CC21" s="2">
-        <f t="shared" si="25"/>
-        <v>4715.8507909608943</v>
+        <f t="shared" si="109"/>
+        <v>5416.9175107400233</v>
       </c>
       <c r="CD21" s="2">
-        <f t="shared" si="25"/>
-        <v>4668.6922830512849</v>
+        <f t="shared" si="109"/>
+        <v>5362.7483356326229</v>
       </c>
       <c r="CE21" s="2">
-        <f t="shared" si="25"/>
-        <v>4622.0053602207718</v>
+        <f t="shared" si="109"/>
+        <v>5309.1208522762963</v>
       </c>
       <c r="CF21" s="2">
-        <f t="shared" si="25"/>
-        <v>4575.7853066185644</v>
+        <f t="shared" si="109"/>
+        <v>5256.0296437535335</v>
       </c>
       <c r="CG21" s="2">
-        <f t="shared" si="25"/>
-        <v>4530.0274535523786</v>
+        <f t="shared" si="109"/>
+        <v>5203.4693473159978</v>
       </c>
       <c r="CH21" s="2">
-        <f t="shared" si="25"/>
-        <v>4484.7271790168552</v>
+        <f t="shared" si="109"/>
+        <v>5151.4346538428381</v>
       </c>
       <c r="CI21" s="2">
-        <f t="shared" si="25"/>
-        <v>4439.8799072266866</v>
+        <f t="shared" si="109"/>
+        <v>5099.92030730441</v>
       </c>
       <c r="CJ21" s="2">
-        <f t="shared" si="25"/>
-        <v>4395.4811081544194</v>
+        <f t="shared" si="109"/>
+        <v>5048.9211042313655</v>
       </c>
       <c r="CK21" s="2">
-        <f t="shared" si="25"/>
-        <v>4351.5262970728754</v>
+        <f t="shared" si="109"/>
+        <v>4998.4318931890521</v>
       </c>
       <c r="CL21" s="2">
-        <f t="shared" si="25"/>
-        <v>4308.0110341021464</v>
+        <f t="shared" si="109"/>
+        <v>4948.4475742571612</v>
       </c>
       <c r="CM21" s="2">
-        <f t="shared" si="25"/>
-        <v>4264.9309237611251</v>
+        <f t="shared" si="109"/>
+        <v>4898.9630985145895</v>
       </c>
       <c r="CN21" s="2">
-        <f t="shared" si="25"/>
-        <v>4222.2816145235138</v>
+        <f t="shared" si="109"/>
+        <v>4849.973467529444</v>
       </c>
       <c r="CO21" s="2">
-        <f t="shared" si="25"/>
-        <v>4180.0587983782789</v>
+        <f t="shared" si="109"/>
+        <v>4801.4737328541496</v>
       </c>
       <c r="CP21" s="2">
-        <f t="shared" si="25"/>
-        <v>4138.258210394496</v>
+        <f t="shared" si="109"/>
+        <v>4753.4589955256079</v>
       </c>
       <c r="CQ21" s="2">
-        <f t="shared" si="25"/>
-        <v>4096.8756282905506</v>
+        <f t="shared" si="109"/>
+        <v>4705.9244055703521</v>
       </c>
       <c r="CR21" s="2">
-        <f t="shared" si="25"/>
-        <v>4055.9068720076452</v>
+        <f t="shared" si="109"/>
+        <v>4658.8651615146482</v>
       </c>
       <c r="CS21" s="2">
-        <f t="shared" si="25"/>
-        <v>4015.3478032875687</v>
+        <f t="shared" si="109"/>
+        <v>4612.2765098995014</v>
       </c>
       <c r="CT21" s="2">
-        <f t="shared" si="25"/>
-        <v>3975.194325254693</v>
+        <f t="shared" si="109"/>
+        <v>4566.1537448005065</v>
       </c>
       <c r="CU21" s="2">
-        <f t="shared" si="25"/>
-        <v>3935.4423820021461</v>
+        <f t="shared" si="109"/>
+        <v>4520.4922073525013</v>
       </c>
       <c r="CV21" s="2">
-        <f t="shared" si="25"/>
-        <v>3896.0879581821246</v>
+        <f t="shared" si="109"/>
+        <v>4475.287285278976</v>
       </c>
       <c r="CW21" s="2">
-        <f t="shared" si="25"/>
-        <v>3857.1270786003033</v>
+        <f t="shared" si="109"/>
+        <v>4430.5344124261865</v>
       </c>
       <c r="CX21" s="2">
-        <f t="shared" ref="CX21:EF21" si="26">CW21*(1+$AM$26)</f>
-        <v>3818.5558078143004</v>
+        <f t="shared" ref="CX21:EF21" si="110">CW21*(1+$AM$26)</f>
+        <v>4386.2290683019246</v>
       </c>
       <c r="CY21" s="2">
-        <f t="shared" si="26"/>
-        <v>3780.3702497361573</v>
+        <f t="shared" si="110"/>
+        <v>4342.366777618905</v>
       </c>
       <c r="CZ21" s="2">
-        <f t="shared" si="26"/>
-        <v>3742.5665472387959</v>
+        <f t="shared" si="110"/>
+        <v>4298.9431098427158</v>
       </c>
       <c r="DA21" s="2">
-        <f t="shared" si="26"/>
-        <v>3705.1408817664078</v>
+        <f t="shared" si="110"/>
+        <v>4255.9536787442885</v>
       </c>
       <c r="DB21" s="2">
-        <f t="shared" si="26"/>
-        <v>3668.0894729487436</v>
+        <f t="shared" si="110"/>
+        <v>4213.3941419568455</v>
       </c>
       <c r="DC21" s="2">
-        <f t="shared" si="26"/>
-        <v>3631.408578219256</v>
+        <f t="shared" si="110"/>
+        <v>4171.2602005372773</v>
       </c>
       <c r="DD21" s="2">
-        <f t="shared" si="26"/>
-        <v>3595.0944924370633</v>
+        <f t="shared" si="110"/>
+        <v>4129.5475985319044</v>
       </c>
       <c r="DE21" s="2">
-        <f t="shared" si="26"/>
-        <v>3559.1435475126927</v>
+        <f t="shared" si="110"/>
+        <v>4088.2521225465853</v>
       </c>
       <c r="DF21" s="2">
-        <f t="shared" si="26"/>
-        <v>3523.5521120375656</v>
+        <f t="shared" si="110"/>
+        <v>4047.3696013211193</v>
       </c>
       <c r="DG21" s="2">
-        <f t="shared" si="26"/>
-        <v>3488.3165909171898</v>
+        <f t="shared" si="110"/>
+        <v>4006.8959053079079</v>
       </c>
       <c r="DH21" s="2">
-        <f t="shared" si="26"/>
-        <v>3453.4334250080178</v>
+        <f t="shared" si="110"/>
+        <v>3966.8269462548287</v>
       </c>
       <c r="DI21" s="2">
-        <f t="shared" si="26"/>
-        <v>3418.8990907579378</v>
+        <f t="shared" si="110"/>
+        <v>3927.1586767922804</v>
       </c>
       <c r="DJ21" s="2">
-        <f t="shared" si="26"/>
-        <v>3384.7100998503583</v>
+        <f t="shared" si="110"/>
+        <v>3887.8870900243573</v>
       </c>
       <c r="DK21" s="2">
-        <f t="shared" si="26"/>
-        <v>3350.8629988518546</v>
+        <f t="shared" si="110"/>
+        <v>3849.0082191241136</v>
       </c>
       <c r="DL21" s="2">
-        <f t="shared" si="26"/>
-        <v>3317.3543688633363</v>
+        <f t="shared" si="110"/>
+        <v>3810.5181369328725</v>
       </c>
       <c r="DM21" s="2">
-        <f t="shared" si="26"/>
-        <v>3284.1808251747029</v>
+        <f t="shared" si="110"/>
+        <v>3772.4129555635436</v>
       </c>
       <c r="DN21" s="2">
-        <f t="shared" si="26"/>
-        <v>3251.339016922956</v>
+        <f t="shared" si="110"/>
+        <v>3734.6888260079081</v>
       </c>
       <c r="DO21" s="2">
-        <f t="shared" si="26"/>
-        <v>3218.8256267537263</v>
+        <f t="shared" si="110"/>
+        <v>3697.341937747829</v>
       </c>
       <c r="DP21" s="2">
-        <f t="shared" si="26"/>
-        <v>3186.637370486189</v>
+        <f t="shared" si="110"/>
+        <v>3660.3685183703506</v>
       </c>
       <c r="DQ21" s="2">
-        <f t="shared" si="26"/>
-        <v>3154.7709967813271</v>
+        <f t="shared" si="110"/>
+        <v>3623.7648331866471</v>
       </c>
       <c r="DR21" s="2">
-        <f t="shared" si="26"/>
-        <v>3123.2232868135138</v>
+        <f t="shared" si="110"/>
+        <v>3587.5271848547804</v>
       </c>
       <c r="DS21" s="2">
-        <f t="shared" si="26"/>
-        <v>3091.9910539453786</v>
+        <f t="shared" si="110"/>
+        <v>3551.6519130062325</v>
       </c>
       <c r="DT21" s="2">
-        <f t="shared" si="26"/>
-        <v>3061.0711434059249</v>
+        <f t="shared" si="110"/>
+        <v>3516.1353938761699</v>
       </c>
       <c r="DU21" s="2">
-        <f t="shared" si="26"/>
-        <v>3030.4604319718655</v>
+        <f t="shared" si="110"/>
+        <v>3480.9740399374082</v>
       </c>
       <c r="DV21" s="2">
-        <f t="shared" si="26"/>
-        <v>3000.1558276521469</v>
+        <f t="shared" si="110"/>
+        <v>3446.1642995380339</v>
       </c>
       <c r="DW21" s="2">
-        <f t="shared" si="26"/>
-        <v>2970.1542693756255</v>
+        <f t="shared" si="110"/>
+        <v>3411.7026565426536</v>
       </c>
       <c r="DX21" s="2">
-        <f t="shared" si="26"/>
-        <v>2940.4527266818691</v>
+        <f t="shared" si="110"/>
+        <v>3377.5856299772272</v>
       </c>
       <c r="DY21" s="2">
-        <f t="shared" si="26"/>
-        <v>2911.0481994150505</v>
+        <f t="shared" si="110"/>
+        <v>3343.8097736774548</v>
       </c>
       <c r="DZ21" s="2">
-        <f t="shared" si="26"/>
-        <v>2881.9377174208998</v>
+        <f t="shared" si="110"/>
+        <v>3310.3716759406802</v>
       </c>
       <c r="EA21" s="2">
-        <f t="shared" si="26"/>
-        <v>2853.1183402466909</v>
+        <f t="shared" si="110"/>
+        <v>3277.2679591812735</v>
       </c>
       <c r="EB21" s="2">
-        <f t="shared" si="26"/>
-        <v>2824.587156844224</v>
+        <f t="shared" si="110"/>
+        <v>3244.4952795894606</v>
       </c>
       <c r="EC21" s="2">
-        <f t="shared" si="26"/>
-        <v>2796.3412852757815</v>
+        <f t="shared" si="110"/>
+        <v>3212.050326793566</v>
       </c>
       <c r="ED21" s="2">
-        <f t="shared" si="26"/>
-        <v>2768.3778724230237</v>
+        <f t="shared" si="110"/>
+        <v>3179.9298235256301</v>
       </c>
       <c r="EE21" s="2">
-        <f t="shared" si="26"/>
-        <v>2740.6940936987935</v>
+        <f t="shared" si="110"/>
+        <v>3148.130525290374</v>
       </c>
       <c r="EF21" s="2">
-        <f t="shared" si="26"/>
-        <v>2713.2871527618054</v>
+        <f t="shared" si="110"/>
+        <v>3116.6492200374701</v>
       </c>
     </row>
     <row r="22" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C22" s="6">
+        <f>637.5</f>
+        <v>637.5</v>
+      </c>
+      <c r="D22" s="6">
+        <f>637.5</f>
+        <v>637.5</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" ref="G22:R22" si="111">637.5</f>
+        <v>637.5</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="N22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="Q22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
+      <c r="R22" s="6">
+        <f t="shared" si="111"/>
+        <v>637.5</v>
+      </c>
       <c r="T22" s="6">
-        <f t="shared" ref="T22:AJ22" si="27">649.9</f>
+        <f t="shared" ref="T22:Y22" si="112">649.9</f>
         <v>649.9</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="112"/>
         <v>649.9</v>
       </c>
       <c r="V22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="112"/>
         <v>649.9</v>
       </c>
       <c r="W22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="112"/>
         <v>649.9</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="112"/>
         <v>649.9</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="112"/>
         <v>649.9</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" ref="Z22:AJ22" si="113">637.5</f>
+        <v>637.5</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AE22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AG22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AH22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AI22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
       <c r="AJ22" s="6">
-        <f t="shared" si="27"/>
-        <v>649.9</v>
+        <f t="shared" si="113"/>
+        <v>637.5</v>
       </c>
     </row>
     <row r="23" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="C23" s="8">
+        <f t="shared" ref="C23" si="114">C21/C22</f>
+        <v>1.7788235294117647</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" ref="D23" si="115">D21/D22</f>
+        <v>1.9780392156862745</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" ref="G23" si="116">G21/G22</f>
+        <v>2.1866666666666665</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" ref="H23:I23" si="117">H21/H22</f>
+        <v>2.3325490196078431</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="117"/>
+        <v>2.3749019607843138</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" ref="J23:K23" si="118">J21/J22</f>
+        <v>1.9811764705882353</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="118"/>
+        <v>2.2949019607843137</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" ref="L23:M23" si="119">L21/L22</f>
+        <v>2.4219607843137254</v>
+      </c>
+      <c r="M23" s="8">
+        <f t="shared" si="119"/>
+        <v>2.216470588235294</v>
+      </c>
+      <c r="N23" s="8">
+        <f t="shared" ref="N23" si="120">N21/N22</f>
+        <v>2.0156862745098039</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" ref="O23:P23" si="121">O21/O22</f>
+        <v>2.2729411764705882</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="121"/>
+        <v>2.4627450980392158</v>
+      </c>
+      <c r="Q23" s="8">
+        <f t="shared" ref="Q23:R23" si="122">Q21/Q22</f>
+        <v>2.7951110399999997</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="122"/>
+        <v>2.2609173772548998</v>
+      </c>
       <c r="T23" s="8">
-        <f t="shared" ref="T23:Y23" si="28">T21/T22</f>
+        <f t="shared" ref="T23:Y23" si="123">T21/T22</f>
         <v>9.4522234189875363</v>
       </c>
       <c r="U23" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="123"/>
         <v>7.3534389906139408</v>
       </c>
       <c r="V23" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="123"/>
         <v>8.5274657639636864</v>
       </c>
       <c r="W23" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="123"/>
         <v>7.6411755654716114</v>
       </c>
       <c r="X23" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="123"/>
         <v>8.7059547622711193</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="123"/>
         <v>8.778273580550854</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" ref="Z23:AJ23" si="29">Z21/Z22</f>
-        <v>9.4494320203108089</v>
+        <f t="shared" ref="Z23:AJ23" si="124">Z21/Z22</f>
+        <v>9.7917146917647067</v>
       </c>
       <c r="AA23" s="8">
-        <f t="shared" si="29"/>
-        <v>9.7447173499615296</v>
+        <f t="shared" si="124"/>
+        <v>10.156648961003928</v>
       </c>
       <c r="AB23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.046659932253277</v>
+        <f t="shared" si="124"/>
+        <v>10.848023494249418</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.278131235458613</v>
+        <f t="shared" si="124"/>
+        <v>11.542667718602075</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.431383594768937</v>
+        <f t="shared" si="124"/>
+        <v>12.069102785268539</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.587177898611467</v>
+        <f t="shared" si="124"/>
+        <v>12.470335976538848</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.745559754850326</v>
+        <f t="shared" si="124"/>
+        <v>12.64213052370374</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" si="29"/>
-        <v>10.906575631196622</v>
+        <f t="shared" si="124"/>
+        <v>12.816584840088282</v>
       </c>
       <c r="AH23" s="8">
-        <f t="shared" si="29"/>
-        <v>11.070272871882352</v>
+        <f t="shared" si="124"/>
+        <v>12.993744359859596</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="29"/>
-        <v>11.2366997146624</v>
+        <f t="shared" si="124"/>
+        <v>13.173655348256048</v>
       </c>
       <c r="AJ23" s="8">
-        <f t="shared" si="29"/>
-        <v>11.405905308151477</v>
+        <f t="shared" si="124"/>
+        <v>13.356364917432412</v>
       </c>
     </row>
     <row r="25" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="G25" s="10">
+        <f>G3/C3-1</f>
+        <v>2.9028049575994697E-2</v>
+      </c>
+      <c r="H25" s="10">
+        <f>H3/D3-1</f>
+        <v>-3.6355475763016121E-2</v>
+      </c>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10">
+        <f t="shared" ref="K25:L26" si="125">K3/G3-1</f>
+        <v>-7.4484944532487996E-3</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="125"/>
+        <v>5.5891942244992165E-3</v>
+      </c>
+      <c r="M25" s="10">
+        <f>M3/I3-1</f>
+        <v>4.7028916428344392E-2</v>
+      </c>
+      <c r="N25" s="10">
+        <f>N3/J3-1</f>
+        <v>3.2847800237812086E-2</v>
+      </c>
+      <c r="O25" s="10">
+        <f>O3/K3-1</f>
+        <v>6.0993134280696193E-2</v>
+      </c>
+      <c r="P25" s="10">
+        <f>P3/L3-1</f>
+        <v>9.911996294580816E-2</v>
+      </c>
+      <c r="Q25" s="10">
+        <f t="shared" ref="Q25:R26" si="126">Q3/M3-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="R25" s="10">
+        <f t="shared" si="126"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
       <c r="T25" s="10"/>
       <c r="U25" s="10">
-        <f t="shared" ref="U25:Y27" si="30">U3/T3-1</f>
+        <f t="shared" ref="U25:Y27" si="127">U3/T3-1</f>
         <v>-0.10467262658800536</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>3.6625298136394813E-2</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>1.2362048122294578E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>-7.2033898305084998E-3</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>1.9632949210413919E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:Z27" si="31">Z3/Y3-1</f>
+        <f t="shared" ref="Z25:Z27" si="128">Z3/Y3-1</f>
+        <v>8.519806689752274E-2</v>
+      </c>
+      <c r="AA25" s="10">
+        <f t="shared" ref="AA25:AA27" si="129">AA3/Z3-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AB25" s="10">
+        <f t="shared" ref="AB25:AB27" si="130">AB3/AA3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AC25" s="10">
+        <f t="shared" ref="AC25:AC27" si="131">AC3/AB3-1</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AD25" s="10">
+        <f t="shared" ref="AD25:AD27" si="132">AD3/AC3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE25" s="10">
+        <f t="shared" ref="AE25:AE27" si="133">AE3/AD3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF25" s="10">
+        <f t="shared" ref="AF25:AF27" si="134">AF3/AE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AA27" si="32">AA3/Z3-1</f>
+      <c r="AG25" s="10">
+        <f t="shared" ref="AG25:AG27" si="135">AG3/AF3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AB25" s="10">
-        <f t="shared" ref="AB25:AB27" si="33">AB3/AA3-1</f>
+      <c r="AH25" s="10">
+        <f t="shared" ref="AH25:AH27" si="136">AH3/AG3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AC27" si="34">AC3/AB3-1</f>
+      <c r="AI25" s="10">
+        <f t="shared" ref="AI25:AI27" si="137">AI3/AH3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD25" s="10">
-        <f t="shared" ref="AD25:AD27" si="35">AD3/AC3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AE27" si="36">AE3/AD3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AF27" si="37">AF3/AE3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AG25" s="10">
-        <f t="shared" ref="AG25:AG27" si="38">AG3/AF3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AH25" s="10">
-        <f t="shared" ref="AH25:AH27" si="39">AH3/AG3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AI27" si="40">AI3/AH3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AJ27" si="41">AJ3/AI3-1</f>
+        <f t="shared" ref="AJ25:AJ27" si="138">AJ3/AI3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -2838,69 +3996,113 @@
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="G26" s="10">
+        <f t="shared" ref="G26:H26" si="139">G4/C4-1</f>
+        <v>0.1381461675579323</v>
+      </c>
+      <c r="H26" s="10">
+        <f t="shared" si="139"/>
+        <v>0.19215513442044951</v>
+      </c>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10">
+        <f t="shared" si="125"/>
+        <v>0.11276429130775245</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="125"/>
+        <v>0.14602587800369693</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" ref="M26:P26" si="140">M4/I4-1</f>
+        <v>7.5394105551747748E-2</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="140"/>
+        <v>0.15744837758112085</v>
+      </c>
+      <c r="O26" s="10">
+        <f t="shared" si="140"/>
+        <v>0.11787473610133703</v>
+      </c>
+      <c r="P26" s="10">
+        <f t="shared" si="140"/>
+        <v>4.2903225806451672E-2</v>
+      </c>
+      <c r="Q26" s="10">
+        <f t="shared" si="126"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="R26" s="10">
+        <f t="shared" si="126"/>
+        <v>0.10000000000000009</v>
+      </c>
       <c r="T26" s="10"/>
       <c r="U26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>-0.12995594713656389</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>0.10746835443037983</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>8.6524174191336067E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>0.14548706080370288</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>0.12214161079988983</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="31"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="128"/>
+        <v>8.4535559374744329E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="129"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AB26" s="10">
+        <f t="shared" si="130"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AB26" s="10">
-        <f t="shared" si="33"/>
+      <c r="AC26" s="10">
+        <f t="shared" si="131"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AC26" s="10">
-        <f t="shared" si="34"/>
+      <c r="AD26" s="10">
+        <f t="shared" si="132"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AD26" s="10">
-        <f t="shared" si="35"/>
+      <c r="AE26" s="10">
+        <f t="shared" si="133"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF26" s="10">
+        <f t="shared" si="134"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE26" s="10">
-        <f t="shared" si="36"/>
+      <c r="AG26" s="10">
+        <f t="shared" si="135"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF26" s="10">
-        <f t="shared" si="37"/>
+      <c r="AH26" s="10">
+        <f t="shared" si="136"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="38"/>
+      <c r="AI26" s="10">
+        <f t="shared" si="137"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH26" s="10">
-        <f t="shared" si="39"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI26" s="10">
-        <f t="shared" si="40"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="138"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" s="1" t="s">
@@ -2914,70 +4116,114 @@
       <c r="B27" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="G27" s="11">
+        <f>G5/C5-1</f>
+        <v>5.8261700095511015E-2</v>
+      </c>
+      <c r="H27" s="11">
+        <f>H5/D5-1</f>
+        <v>2.1557019993298399E-2</v>
+      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11">
+        <f t="shared" ref="K27:L27" si="141">K5/G5-1</f>
+        <v>2.7188628158844708E-2</v>
+      </c>
+      <c r="L27" s="11">
+        <f t="shared" si="141"/>
+        <v>4.7124425978569917E-2</v>
+      </c>
+      <c r="M27" s="11">
+        <f>M5/I5-1</f>
+        <v>5.6013894919670015E-2</v>
+      </c>
+      <c r="N27" s="11">
+        <f>N5/J5-1</f>
+        <v>6.8644067796610253E-2</v>
+      </c>
+      <c r="O27" s="11">
+        <f>O5/K5-1</f>
+        <v>7.8747940691927587E-2</v>
+      </c>
+      <c r="P27" s="11">
+        <f>P5/L5-1</f>
+        <v>8.092304479482082E-2</v>
+      </c>
+      <c r="Q27" s="11">
+        <f t="shared" ref="Q27:R27" si="142">Q5/M5-1</f>
+        <v>9.3548519736842195E-2</v>
+      </c>
+      <c r="R27" s="11">
+        <f t="shared" si="142"/>
+        <v>8.622323552735911E-2</v>
+      </c>
       <c r="T27" s="11"/>
       <c r="U27" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>-0.11092647579612624</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>5.377332475411345E-2</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>3.1228192602930971E-2</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>3.3722438391699194E-2</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="127"/>
         <v>5.0079100976487823E-2</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" si="31"/>
-        <v>3.2217517793132089E-2</v>
+        <f t="shared" si="128"/>
+        <v>8.4987791573588156E-2</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" si="32"/>
-        <v>2.3283423477244103E-2</v>
+        <f t="shared" si="129"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="33"/>
-        <v>2.0222677069059891E-2</v>
+        <f t="shared" si="130"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" si="34"/>
-        <v>1.6947231155695519E-2</v>
+        <f t="shared" si="131"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" si="35"/>
-        <v>1.3518200291589677E-2</v>
+        <f t="shared" si="132"/>
+        <v>2.9999999999999805E-2</v>
       </c>
       <c r="AE27" s="11">
-        <f t="shared" si="36"/>
-        <v>1.3540700400238359E-2</v>
+        <f t="shared" si="133"/>
+        <v>2.3172608191648347E-2</v>
       </c>
       <c r="AF27" s="11">
-        <f t="shared" si="37"/>
-        <v>1.3563265300364558E-2</v>
+        <f t="shared" si="134"/>
+        <v>1.3193778265011558E-2</v>
       </c>
       <c r="AG27" s="11">
-        <f t="shared" si="38"/>
-        <v>1.358589417237277E-2</v>
+        <f t="shared" si="135"/>
+        <v>1.3215232762177287E-2</v>
       </c>
       <c r="AH27" s="11">
-        <f t="shared" si="39"/>
-        <v>1.3608586185788418E-2</v>
+        <f t="shared" si="136"/>
+        <v>1.3236762843053862E-2</v>
       </c>
       <c r="AI27" s="11">
-        <f t="shared" si="40"/>
-        <v>1.3631340499348665E-2</v>
+        <f t="shared" si="137"/>
+        <v>1.3258367857332143E-2</v>
       </c>
       <c r="AJ27" s="11">
-        <f t="shared" si="41"/>
-        <v>1.3654156261102779E-2</v>
+        <f t="shared" si="138"/>
+        <v>1.3280047142869122E-2</v>
       </c>
       <c r="AL27" s="1" t="s">
         <v>58</v>
@@ -2990,152 +4236,264 @@
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="C28" s="10">
+        <f t="shared" ref="C28" si="143">(C3-C6)/C3</f>
+        <v>0.33806262230919765</v>
+      </c>
+      <c r="D28" s="10">
+        <f t="shared" ref="D28" si="144">(D3-D6)/D3</f>
+        <v>0.35233393177737882</v>
+      </c>
+      <c r="G28" s="10">
+        <f t="shared" ref="G28" si="145">(G3-G6)/G3</f>
+        <v>0.35530903328050711</v>
+      </c>
+      <c r="H28" s="10">
+        <f t="shared" ref="H28:I28" si="146">(H3-H6)/H3</f>
+        <v>0.35832945194845522</v>
+      </c>
+      <c r="I28" s="10">
+        <f t="shared" si="146"/>
+        <v>0.35017476962186211</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" ref="J28:K28" si="147">(J3-J6)/J3</f>
+        <v>0.3035077288941736</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="147"/>
+        <v>0.35574006067379849</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" ref="L28:M29" si="148">(L3-L6)/L3</f>
+        <v>0.34429519839431838</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="148"/>
+        <v>0.3678300455235205</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" ref="N28" si="149">(N3-N6)/N3</f>
+        <v>0.31227514750323787</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" ref="O28:P28" si="150">(O3-O6)/O3</f>
+        <v>0.36027088036117383</v>
+      </c>
+      <c r="P28" s="10">
+        <f t="shared" si="150"/>
+        <v>0.36114622840286559</v>
+      </c>
+      <c r="Q28" s="10">
+        <f t="shared" ref="Q28:R28" si="151">(Q3-Q6)/Q3</f>
+        <v>0.36</v>
+      </c>
+      <c r="R28" s="10">
+        <f t="shared" si="151"/>
+        <v>0.31999999999999995</v>
+      </c>
       <c r="T28" s="10">
-        <f t="shared" ref="T28:Y29" si="42">(T3-T6)/T3</f>
+        <f t="shared" ref="T28:Y29" si="152">(T3-T6)/T3</f>
         <v>0.30258062181041662</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.28697901928285563</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.28463908279062511</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.34687981510015409</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.34128739378419276</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.34445755165721681</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" ref="Z28:AJ28" si="43">(Z3-Z6)/Z3</f>
+        <f t="shared" ref="Z28:AJ28" si="153">(Z3-Z6)/Z3</f>
+        <v>0.34982265186240785</v>
+      </c>
+      <c r="AA28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.34</v>
+      </c>
+      <c r="AB28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.34</v>
+      </c>
+      <c r="AC28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.34</v>
+      </c>
+      <c r="AD28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="AE28" s="10">
+        <f t="shared" si="153"/>
         <v>0.33999999999999991</v>
       </c>
-      <c r="AA28" s="10">
-        <f t="shared" si="43"/>
+      <c r="AF28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.33999999999999991</v>
+      </c>
+      <c r="AG28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.34</v>
+      </c>
+      <c r="AH28" s="10">
+        <f t="shared" si="153"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="AB28" s="10">
-        <f t="shared" si="43"/>
+      <c r="AI28" s="10">
+        <f t="shared" si="153"/>
+        <v>0.34</v>
+      </c>
+      <c r="AJ28" s="10">
+        <f t="shared" si="153"/>
         <v>0.33999999999999997</v>
-      </c>
-      <c r="AC28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="AD28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.34</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="AF28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="AG28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.34</v>
-      </c>
-      <c r="AH28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.34</v>
-      </c>
-      <c r="AI28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.33999999999999991</v>
-      </c>
-      <c r="AJ28" s="10">
-        <f t="shared" si="43"/>
-        <v>0.33999999999999991</v>
       </c>
       <c r="AL28" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AM28" s="6">
         <f>NPV(AM27,Z21:EF21)</f>
-        <v>108619.57438714338</v>
+        <v>122572.85753670074</v>
       </c>
     </row>
     <row r="29" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="C29" s="10">
+        <f t="shared" ref="C29" si="154">(C4-C7)/C4</f>
+        <v>0.43627450980392157</v>
+      </c>
+      <c r="D29" s="10">
+        <f t="shared" ref="D29" si="155">(D4-D7)/D4</f>
+        <v>0.4133979726751873</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" ref="G29" si="156">(G4-G7)/G4</f>
+        <v>0.44009397024275648</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" ref="H29:I29" si="157">(H4-H7)/H4</f>
+        <v>0.44805914972273569</v>
+      </c>
+      <c r="I29" s="10">
+        <f t="shared" si="157"/>
+        <v>0.45853324194653872</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" ref="J29:K29" si="158">(J4-J7)/J4</f>
+        <v>0.4413716814159292</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="158"/>
+        <v>0.45531315974665726</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="148"/>
+        <v>0.48096774193548386</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="148"/>
+        <v>0.42224346717654559</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" ref="N29" si="159">(N4-N7)/N4</f>
+        <v>0.47785919082510353</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" ref="O29:P29" si="160">(O4-O7)/O4</f>
+        <v>0.43783443500157382</v>
+      </c>
+      <c r="P29" s="10">
+        <f t="shared" si="160"/>
+        <v>0.44911846582121867</v>
+      </c>
+      <c r="Q29" s="10">
+        <f t="shared" ref="Q29:R29" si="161">(Q4-Q7)/Q4</f>
+        <v>0.45999999999999996</v>
+      </c>
+      <c r="R29" s="10">
+        <f t="shared" si="161"/>
+        <v>0.45999999999999996</v>
+      </c>
       <c r="T29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.44162995594713655</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.42645569620253165</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.42279117613441536</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.43277929728592468</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.44733217007989712</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="152"/>
         <v>0.45912104100171863</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" ref="Z29:AJ29" si="44">(Z4-Z7)/Z4</f>
+        <f t="shared" ref="Z29:AJ29" si="162">(Z4-Z7)/Z4</f>
+        <v>0.45203135540909484</v>
+      </c>
+      <c r="AA29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AB29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AC29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AD29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AE29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AF29" s="10">
+        <f t="shared" si="162"/>
+        <v>0.47</v>
+      </c>
+      <c r="AG29" s="10">
+        <f t="shared" si="162"/>
         <v>0.46999999999999992</v>
       </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="44"/>
+      <c r="AH29" s="10">
+        <f t="shared" si="162"/>
         <v>0.47000000000000003</v>
       </c>
-      <c r="AB29" s="10">
-        <f t="shared" si="44"/>
+      <c r="AI29" s="10">
+        <f t="shared" si="162"/>
         <v>0.47000000000000003</v>
       </c>
-      <c r="AC29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
-      <c r="AD29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.46999999999999992</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
-      <c r="AF29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
-      <c r="AG29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
-      <c r="AH29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
-      <c r="AI29" s="10">
-        <f t="shared" si="44"/>
-        <v>0.47</v>
-      </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="162"/>
         <v>0.47</v>
       </c>
       <c r="AL29" s="1" t="s">
@@ -3143,92 +4501,192 @@
       </c>
       <c r="AM29" s="6">
         <f>Main!D8</f>
-        <v>-20146</v>
+        <v>-24408</v>
       </c>
     </row>
     <row r="30" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="C30" s="10">
+        <f t="shared" ref="C30" si="163">C9/C5</f>
+        <v>0.36437440305635149</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" ref="D30" si="164">D9/D5</f>
+        <v>0.36780967273539594</v>
+      </c>
+      <c r="G30" s="10">
+        <f t="shared" ref="G30" si="165">G9/G5</f>
+        <v>0.37973826714801445</v>
+      </c>
+      <c r="H30" s="10">
+        <f t="shared" ref="H30:I30" si="166">H9/H5</f>
+        <v>0.38486770172753115</v>
+      </c>
+      <c r="I30" s="10">
+        <f t="shared" si="166"/>
+        <v>0.38449848024316108</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" ref="J30:K30" si="167">J9/J5</f>
+        <v>0.34311440677966104</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="167"/>
+        <v>0.3868204283360791</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" ref="L30:M30" si="168">L9/L5</f>
+        <v>0.38853503184713378</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="168"/>
+        <v>0.38538240131578949</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" ref="N30" si="169">N9/N5</f>
+        <v>0.36379857256145914</v>
+      </c>
+      <c r="O30" s="10">
+        <f t="shared" ref="O30:P30" si="170">O9/O5</f>
+        <v>0.38535939727143148</v>
+      </c>
+      <c r="P30" s="10">
+        <f t="shared" si="170"/>
+        <v>0.3886205564142195</v>
+      </c>
+      <c r="Q30" s="10">
+        <f t="shared" ref="Q30:R30" si="171">Q9/Q5</f>
+        <v>0.39185774823181707</v>
+      </c>
+      <c r="R30" s="10">
+        <f t="shared" si="171"/>
+        <v>0.3641151615923604</v>
+      </c>
       <c r="T30" s="10">
-        <f t="shared" ref="T30:Y30" si="45">T9/T5</f>
+        <f t="shared" ref="T30:Y30" si="172">T9/T5</f>
         <v>0.3369745838895094</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="172"/>
         <v>0.32074026411741274</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="172"/>
         <v>0.31978367062107466</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="172"/>
         <v>0.36990356961597021</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="172"/>
         <v>0.3727838088483989</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="172"/>
         <v>0.38085095329627511</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" ref="Z30:AJ30" si="46">Z9/Z5</f>
-        <v>0.38317112630104283</v>
+        <f t="shared" ref="Z30:AJ30" si="173">Z9/Z5</f>
+        <v>0.3822494688754044</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38429826729925837</v>
+        <f t="shared" si="173"/>
+        <v>0.38124390649142709</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38515700251202145</v>
+        <f t="shared" si="173"/>
+        <v>0.38124390649142714</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.3857366037906651</v>
+        <f t="shared" si="173"/>
+        <v>0.38124390649142709</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38602910520310035</v>
+        <f t="shared" si="173"/>
+        <v>0.38124390649142703</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38632244890473788</v>
+        <f t="shared" si="173"/>
+        <v>0.38151911744515032</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38661662424084664</v>
+        <f t="shared" si="173"/>
+        <v>0.38179802590830392</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38691162041524746</v>
+        <f t="shared" si="173"/>
+        <v>0.38207791695970011</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38720742649153322</v>
+        <f t="shared" si="173"/>
+        <v>0.38235878214531593</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38750403139433587</v>
+        <f t="shared" si="173"/>
+        <v>0.38264061285729817</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="46"/>
-        <v>0.38780142391064343</v>
+        <f t="shared" si="173"/>
+        <v>0.38292340033447009</v>
       </c>
       <c r="AL30" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AM30" s="6">
         <f>AM28+AM29</f>
-        <v>88473.574387143381</v>
+        <v>98164.857536700743</v>
       </c>
     </row>
     <row r="31" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="G31" s="10">
+        <f>G10/C10-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="H31" s="10">
+        <f t="shared" ref="H31:O31" si="174">H10/D10-1</f>
+        <v>-2.8497409326424861E-2</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10">
+        <f t="shared" si="174"/>
+        <v>8.4033613445377853E-3</v>
+      </c>
+      <c r="L31" s="10">
+        <f t="shared" si="174"/>
+        <v>1.8666666666666609E-2</v>
+      </c>
+      <c r="M31" s="10">
+        <f t="shared" si="174"/>
+        <v>1.098901098901095E-2</v>
+      </c>
+      <c r="N31" s="10">
+        <f t="shared" si="174"/>
+        <v>0.18333333333333335</v>
+      </c>
+      <c r="O31" s="10">
+        <f t="shared" si="174"/>
+        <v>0.21944444444444455</v>
+      </c>
+      <c r="P31" s="10">
+        <f>P10/L10-1</f>
+        <v>0.25916230366492155</v>
+      </c>
+      <c r="Q31" s="10">
+        <f t="shared" ref="Q31:R32" si="175">Q10/M10-1</f>
+        <v>0.25</v>
+      </c>
+      <c r="R31" s="10">
+        <f t="shared" si="175"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
@@ -3243,47 +4701,47 @@
         <v>5.4945054945054972E-2</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" ref="Z31:AJ31" si="47">Z10/Y10-1</f>
+        <f t="shared" ref="Z31:AJ31" si="176">Z10/Y10-1</f>
+        <v>0.23124999999999996</v>
+      </c>
+      <c r="AA31" s="10">
+        <f t="shared" si="176"/>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AB31" s="10">
+        <f t="shared" si="176"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AC31" s="10">
+        <f t="shared" si="176"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AA31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AD31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AE31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AF31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AG31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AH31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF31" s="10">
-        <f t="shared" si="47"/>
+      <c r="AI31" s="10">
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG31" s="10">
-        <f t="shared" si="47"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH31" s="10">
-        <f t="shared" si="47"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI31" s="10">
-        <f t="shared" si="47"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AJ31" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="176"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL31" s="1" t="s">
@@ -3291,24 +4749,68 @@
       </c>
       <c r="AM31" s="5">
         <f>AM30/AJ22</f>
-        <v>136.1341350779249</v>
+        <v>153.98409025364822</v>
       </c>
     </row>
     <row r="32" spans="2:136" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="G32" s="10">
+        <f t="shared" ref="G32:P32" si="177">G11/C11-1</f>
+        <v>-7.9664570230607912E-2</v>
+      </c>
+      <c r="H32" s="10">
+        <f t="shared" si="177"/>
+        <v>-3.3690658499234249E-2</v>
+      </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10">
+        <f t="shared" si="177"/>
+        <v>-1.1389521640091105E-2</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="177"/>
+        <v>7.844690966719492E-2</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="177"/>
+        <v>0.11661341853035134</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="177"/>
+        <v>8.4104938271605034E-2</v>
+      </c>
+      <c r="O32" s="10">
+        <f t="shared" si="177"/>
+        <v>4.5314900153609727E-2</v>
+      </c>
+      <c r="P32" s="10">
+        <f t="shared" si="177"/>
+        <v>4.9228508449669306E-2</v>
+      </c>
+      <c r="Q32" s="10">
+        <f t="shared" si="175"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="R32" s="10">
+        <f t="shared" si="175"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
       <c r="T32" s="10"/>
       <c r="U32" s="10">
-        <f t="shared" ref="U32:W32" si="48">U11/T11-1</f>
+        <f t="shared" ref="U32:W32" si="178">U11/T11-1</f>
         <v>-0.13535060699402068</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="178"/>
         <v>5.4484492875104262E-3</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="178"/>
         <v>8.6702792830345876E-2</v>
       </c>
       <c r="X32" s="10">
@@ -3320,47 +4822,47 @@
         <v>6.6120538326506662E-2</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" ref="Z32:AJ32" si="49">Z11/Y11-1</f>
+        <f t="shared" ref="Z32:AJ32" si="179">Z11/Y11-1</f>
+        <v>4.8691913648005736E-2</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" si="179"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AB32" s="10">
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AC32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AD32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AE32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AF32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AG32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AH32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH32" s="10">
-        <f t="shared" si="49"/>
+      <c r="AI32" s="10">
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI32" s="10">
-        <f t="shared" si="49"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="179"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL32" s="1" t="s">
@@ -3368,111 +4870,223 @@
       </c>
       <c r="AM32" s="5">
         <f>Main!D3</f>
-        <v>227</v>
+        <v>214.25</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="C33" s="10">
+        <f t="shared" ref="C33" si="180">C14/C5</f>
+        <v>0.15174307545367718</v>
+      </c>
+      <c r="D33" s="10">
+        <f t="shared" ref="D33" si="181">D14/D5</f>
+        <v>0.17882274098067688</v>
+      </c>
+      <c r="G33" s="10">
+        <f t="shared" ref="G33" si="182">G14/G5</f>
+        <v>0.19088447653429602</v>
+      </c>
+      <c r="H33" s="10">
+        <f t="shared" ref="H33:I33" si="183">H14/H5</f>
+        <v>0.20588235294117646</v>
+      </c>
+      <c r="I33" s="10">
+        <f t="shared" si="183"/>
+        <v>0.20907511940946591</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" ref="J33:K33" si="184">J14/J5</f>
+        <v>0.16769067796610168</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="184"/>
+        <v>0.2042833607907743</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" ref="L33:M33" si="185">L14/L5</f>
+        <v>0.20653649368278165</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="185"/>
+        <v>0.19099506578947367</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" ref="N33" si="186">N14/N5</f>
+        <v>0.17297779540047581</v>
+      </c>
+      <c r="O33" s="10">
+        <f t="shared" ref="O33:P33" si="187">O14/O5</f>
+        <v>0.20057014864589698</v>
+      </c>
+      <c r="P33" s="10">
+        <f t="shared" si="187"/>
+        <v>0.20421174652241114</v>
+      </c>
+      <c r="Q33" s="10">
+        <f t="shared" ref="Q33:R33" si="188">Q14/Q5</f>
+        <v>0.21063075528950817</v>
+      </c>
+      <c r="R33" s="10">
+        <f t="shared" si="188"/>
+        <v>0.18283366582039115</v>
+      </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:Y33" si="50">T14/T5</f>
+        <f t="shared" ref="T33:Y33" si="189">T14/T5</f>
         <v>0.18662998174834508</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="189"/>
         <v>0.17452584489996018</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="189"/>
         <v>0.18027448243777622</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="189"/>
         <v>0.18121581232729939</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="189"/>
         <v>0.19322459222082811</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="189"/>
         <v>0.19328276793599666</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" ref="Z33:AJ33" si="51">Z14/Z5</f>
-        <v>0.20168228090223245</v>
+        <f t="shared" ref="Z33:AJ33" si="190">Z14/Z5</f>
+        <v>0.19938196584810197</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20339176763396466</v>
+        <f t="shared" si="190"/>
+        <v>0.20005660071098125</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20567421317535112</v>
+        <f t="shared" si="190"/>
+        <v>0.20295530963095837</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.2070897947823194</v>
+        <f t="shared" si="190"/>
+        <v>0.20716073598949453</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20760978463666452</v>
+        <f t="shared" si="190"/>
+        <v>0.21007223475963815</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20813127185758981</v>
+        <f t="shared" si="190"/>
+        <v>0.21208385386570563</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20865423750381215</v>
+        <f t="shared" si="190"/>
+        <v>0.21242641167928383</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20917866238259122</v>
+        <f t="shared" si="190"/>
+        <v>0.21277017631633457</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.20970452705189876</v>
+        <f t="shared" si="190"/>
+        <v>0.21311513739355287</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.21023181182267081</v>
+        <f t="shared" si="190"/>
+        <v>0.21346128433869824</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="51"/>
-        <v>0.21076049676114908</v>
+        <f t="shared" si="190"/>
+        <v>0.21380860639121674</v>
       </c>
       <c r="AL33" s="2" t="s">
         <v>64</v>
       </c>
       <c r="AM33" s="11">
         <f>AM31/AM32-1</f>
-        <v>-0.4002901538417406</v>
+        <v>-0.28128779344854971</v>
       </c>
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="C34" s="10">
+        <f>C19/C18</f>
+        <v>0.24651162790697675</v>
+      </c>
+      <c r="D34" s="10">
+        <f>D19/D18</f>
+        <v>0.25880281690140844</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" ref="G34:P34" si="191">G19/G18</f>
+        <v>0.20987654320987653</v>
+      </c>
+      <c r="H34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.21165966386554622</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.22979156075241486</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.17131474103585656</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.21165152324959915</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.20972644376899696</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.22423245614035087</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.16450777202072539</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.2213375796178344</v>
+      </c>
+      <c r="P34" s="10">
+        <f t="shared" si="191"/>
+        <v>0.16141101015499731</v>
+      </c>
+      <c r="Q34" s="10">
+        <f t="shared" ref="Q34:R34" si="192">Q19/Q18</f>
+        <v>0.18</v>
+      </c>
+      <c r="R34" s="10">
+        <f t="shared" si="192"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="T34" s="10">
-        <f t="shared" ref="T34:X34" si="52">T19/T18</f>
+        <f t="shared" ref="T34:X34" si="193">T19/T18</f>
         <v>0.1758169069982802</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="193"/>
         <v>0.19078509647371922</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="193"/>
         <v>0.22460262612301313</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="193"/>
         <v>0.22135130898259917</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="193"/>
         <v>0.20771057410252827</v>
       </c>
       <c r="Y34" s="10">
@@ -3480,47 +5094,47 @@
         <v>0.20421461250519896</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" ref="Z34:AJ34" si="53">Z19/Z18</f>
+        <f t="shared" ref="Z34:AJ34" si="194">Z19/Z18</f>
+        <v>0.18560777786038365</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AB34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AB34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AC34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AD34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AE34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AF34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="53"/>
+      <c r="AG34" s="10">
+        <f t="shared" si="194"/>
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="AH34" s="10">
+        <f t="shared" si="194"/>
+        <v>0.20999999999999996</v>
+      </c>
+      <c r="AI34" s="10">
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
-      <c r="AG34" s="10">
-        <f t="shared" si="53"/>
-        <v>0.21</v>
-      </c>
-      <c r="AH34" s="10">
-        <f t="shared" si="53"/>
-        <v>0.21</v>
-      </c>
-      <c r="AI34" s="10">
-        <f t="shared" si="53"/>
-        <v>0.21</v>
-      </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="194"/>
         <v>0.21</v>
       </c>
       <c r="AL34" s="1" t="s">
@@ -3534,73 +5148,129 @@
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="C35" s="10">
+        <f t="shared" ref="C35" si="195">C21/C5</f>
+        <v>0.13538681948424069</v>
+      </c>
+      <c r="D35" s="10">
+        <f t="shared" ref="D35" si="196">D21/D5</f>
+        <v>0.14084664358315649</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" ref="G35" si="197">G21/G5</f>
+        <v>0.1572653429602888</v>
+      </c>
+      <c r="H35" s="10">
+        <f t="shared" ref="H35:I35" si="198">H21/H5</f>
+        <v>0.16258473649682922</v>
+      </c>
+      <c r="I35" s="10">
+        <f t="shared" si="198"/>
+        <v>0.16435084672166739</v>
+      </c>
+      <c r="J35" s="10">
+        <f t="shared" ref="J35:K35" si="199">J21/J5</f>
+        <v>0.13379237288135593</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="199"/>
+        <v>0.16068094453596926</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" ref="L35:M35" si="200">L21/L5</f>
+        <v>0.16121958859768196</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="200"/>
+        <v>0.14525082236842105</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" ref="N35" si="201">N21/N5</f>
+        <v>0.12737906423473433</v>
+      </c>
+      <c r="O35" s="10">
+        <f t="shared" ref="O35:P35" si="202">O21/O5</f>
+        <v>0.14752596212583996</v>
+      </c>
+      <c r="P35" s="10">
+        <f t="shared" si="202"/>
+        <v>0.151661514683153</v>
+      </c>
+      <c r="Q35" s="10">
+        <f t="shared" ref="Q35:R35" si="203">Q21/Q5</f>
+        <v>0.16750108929840457</v>
+      </c>
+      <c r="R35" s="10">
+        <f t="shared" si="203"/>
+        <v>0.13153481513658727</v>
+      </c>
       <c r="T35" s="10">
-        <f t="shared" ref="T35:Y35" si="54">T21/T5</f>
+        <f t="shared" ref="T35:Y35" si="204">T21/T5</f>
         <v>0.16734315835353727</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="204"/>
         <v>0.14642889971504733</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="204"/>
         <v>0.16114212607583159</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="204"/>
         <v>0.14002142897422884</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="204"/>
         <v>0.15432873274780426</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="204"/>
         <v>0.1481895163385111</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" ref="Z35:AJ35" si="55">Z21/Z5</f>
-        <v>0.15454069058296629</v>
+        <f t="shared" ref="Z35:AJ35" si="205">Z21/Z5</f>
+        <v>0.14944311798028534</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15574368687287801</v>
+        <f t="shared" si="205"/>
+        <v>0.14623850769565919</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15738666549819816</v>
+        <f t="shared" si="205"/>
+        <v>0.14875535962767356</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15832954820425235</v>
+        <f t="shared" si="205"/>
+        <v>0.15219306366780838</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15854705446243489</v>
+        <f t="shared" si="205"/>
+        <v>0.15449926832986186</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15876518705322612</v>
+        <f t="shared" si="205"/>
+        <v>0.15602014982399307</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.1589839380536876</v>
+        <f t="shared" si="205"/>
+        <v>0.15610984475188275</v>
       </c>
       <c r="AG35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.159203299435699</v>
+        <f t="shared" si="205"/>
+        <v>0.15619985567298614</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15942326306686552</v>
+        <f t="shared" si="205"/>
+        <v>0.15629017986855073</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15964382071145969</v>
+        <f t="shared" si="205"/>
+        <v>0.1563808145703541</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="55"/>
-        <v>0.15986496403140135</v>
+        <f t="shared" si="205"/>
+        <v>0.15647175696086543</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/HON.xlsx
+++ b/Financial Analysis/HON.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74657B5-88B4-4F64-98D6-D66596CE543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296619D6-471E-40F6-B61D-8A31882A334C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F30574C2-14C5-4405-B92F-D72ACFF190E8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>HON</t>
   </si>
@@ -227,16 +227,26 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +279,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -315,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -334,6 +353,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,14 +801,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>214.25</v>
+        <v>209.05</v>
       </c>
       <c r="E3" s="4">
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="4">
         <v>45953</v>
@@ -811,7 +832,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>136584.375</v>
+        <v>133269.375</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -853,7 +874,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>160992.375</v>
+        <v>157677.375</v>
       </c>
     </row>
   </sheetData>
@@ -863,7 +884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1001FB57-91F3-4052-BB69-223C5CE863B6}">
-  <dimension ref="B2:EF35"/>
+  <dimension ref="B2:EF42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -4870,7 +4891,7 @@
       </c>
       <c r="AM32" s="5">
         <f>Main!D3</f>
-        <v>214.25</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.3">
@@ -5006,7 +5027,7 @@
       </c>
       <c r="AM33" s="11">
         <f>AM31/AM32-1</f>
-        <v>-0.28128779344854971</v>
+        <v>-0.26341023557212051</v>
       </c>
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.3">
@@ -5271,6 +5292,35 @@
       <c r="AJ35" s="10">
         <f t="shared" si="205"/>
         <v>0.15647175696086543</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N39" s="12">
+        <v>75196</v>
+      </c>
+      <c r="P39" s="12">
+        <v>78419</v>
+      </c>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P41" s="13">
+        <f>Main!D9/Model!P39</f>
+        <v>2.0107037197617923</v>
+      </c>
+    </row>
+    <row r="42" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P42" s="10">
+        <f>P39/Main!D9-1</f>
+        <v>-0.50266168497541264</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/HON.xlsx
+++ b/Financial Analysis/HON.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA89C72-9233-46DB-A56C-F34230BCCA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB9ABBA-2B64-41BB-A920-7934BF52CFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{F30574C2-14C5-4405-B92F-D72ACFF190E8}"/>
   </bookViews>
@@ -853,14 +853,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>216.14</v>
+        <v>190.02</v>
       </c>
       <c r="E3" s="4">
-        <v>45955</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45955</v>
+        <v>46002</v>
       </c>
       <c r="G3" s="4">
         <v>46051</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>137227.28599999999</v>
+        <v>120643.698</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -925,7 +925,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>160905.28599999999</v>
+        <v>144321.698</v>
       </c>
     </row>
   </sheetData>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="AM50" s="5">
         <f>Main!D3</f>
-        <v>216.14</v>
+        <v>190.02</v>
       </c>
     </row>
     <row r="51" spans="2:39" x14ac:dyDescent="0.3">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM51" s="11">
         <f>AM49/AM50-1</f>
-        <v>-0.24758321992099541</v>
+        <v>-0.14415660011432463</v>
       </c>
     </row>
     <row r="52" spans="2:39" x14ac:dyDescent="0.3">
@@ -5711,7 +5711,7 @@
       <c r="P59" s="13"/>
       <c r="Z59" s="13">
         <f>Main!$D$9/Model!Z57</f>
-        <v>1.988522634304287</v>
+        <v>1.7835769739362557</v>
       </c>
     </row>
     <row r="60" spans="2:39" x14ac:dyDescent="0.3">
@@ -5721,7 +5721,7 @@
       <c r="P60" s="10"/>
       <c r="Z60" s="10">
         <f>Z57/Main!$D$9-1</f>
-        <v>-0.49711409729572209</v>
+        <v>-0.43932893583333532</v>
       </c>
     </row>
   </sheetData>
